--- a/data/raw/rules/translations.xlsx
+++ b/data/raw/rules/translations.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="530">
   <si>
     <t xml:space="preserve">key</t>
   </si>
@@ -1342,6 +1342,865 @@
   </si>
   <si>
     <t xml:space="preserve">This Magical Power targets one enemy model that has a Staff of Power within range. The target's Staff of Power is immediately destroyed - remove it from their wargear.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rend.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rend.description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When a &lt;b&gt;Monster&lt;/b&gt; uses this Brutal Power Attack, they must nominate one enemy model involved in the Combat to Rend (if this is a &lt;b&gt;Cavalry&lt;/b&gt; model, you must choose either the rider or the &lt;b&gt;Mount&lt;/b&gt;). The &lt;b&gt;Monster&lt;/b&gt; makes a number of To Wound Rolls equal to its Attacks characteristic (including any modifiers to its Attacks) against the nominated model. When resolving these To Wound Rolls, use the nominated model’s Strength characteristic instead of their Defence when using the To Wound Chart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">barge.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">barge.description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When a &lt;b&gt;Monster&lt;/b&gt; wishes to use this Brutal Power Attack, enemymodelsdo not Back Away as normal. Instead, all enemy models involved in the Combat, plus any enemy models that were Supporting, must Back Away3" rather than 1". The order and direction that these models Back Away is chosen by the &lt;b&gt;Monster&lt;/b&gt; model’s controlling player. Models may still Make Way for losing models (which will be decided by the &lt;b&gt;Monster&lt;/b&gt; model’s controlling player) and, if they do, must Make Way 3" rather than the usual 1", in a direction chosen by the &lt;b&gt;Monster&lt;/b&gt; model’s controlling player.
+Any models that cannot Back Away or Make Way the full 3" are moved as far as possible and then knocked Prone. When doing this, if it is possible for a &lt;b&gt;Monster&lt;/b&gt; to choose a direction for a model to Back Away or Make Way so that it goes the full 3", then it must choose that direction–it can’t force a model to Back Away or Make Way less than 3" and be knocked Prone if there was a way for it to Back Away the full 3".
+Once a &lt;b&gt;Monster&lt;/b&gt; model has used a Barge, the Combat immediately ends and no further Strikes or Brutal Power Attacks can be made.
+Once all models have Backed Away, the &lt;b&gt;Monster&lt;/b&gt; that made the Barge can then Move D3+3" in any direction, following all the usual rules for Moving a model. It can even Charge again if it wishes, in which case it will fight again that Fight Phase in the ordinary way – i.e., in an order chosen by the player with Priority.
+A &lt;b&gt;Monster&lt;/b&gt; cannot Barge in the same turn in which it participates in a Heroic Combat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hurl.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hurl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hurl.description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When a &lt;b&gt;Monster&lt;/b&gt; wishes to use this Brutal Power Attack, it must nominate a single enemy model involved in the Combat before models Back Away – this is the model that will be Hurled. A &lt;b&gt;Monster&lt;/b&gt; cannot nominate a model to be Hurled that has a Strength equal to or higher than their own. Then, all other enemy models (not the nominated model) Back Away as normal. The Monster will then Hurl the nominated model.
+To Hurl a model, follow the steps below:
+&lt;ul&gt;
+&lt;li&gt; The &lt;b&gt;Monster&lt;/b&gt; rolls a D3 and adds the difference in Strength between the &lt;b&gt;Monster&lt;/b&gt; and the nominated model – this is the Hurl Distance.&lt;/li&gt;
+&lt;li&gt;The &lt;b&gt;Monster&lt;/b&gt; must then take an Intelligence Test (if the &lt;b&gt;Monster&lt;/b&gt; is also a &lt;b&gt;Mount&lt;/b&gt;, it may use the Intelligence of its rider if it is better).&lt;/li&gt;
+&lt;li&gt;If the test is passed, the &lt;b&gt;Monster&lt;/b&gt; chooses an enemy model it can draw Line of Sight to, and within the Hurl Distance from itself, to Hurl the nominated model at – this is the target. A model can only be chosen as the target of a Hurl once per turn. If the test was failed, the opposing player may choose one of their models in Line of Sight of the &lt;b&gt;Monster&lt;/b&gt;, and within the Hurl Distance, to be the target instead.&lt;/li&gt;
+&lt;li&gt;The Hurled model suffers two Strength 6 hits (if it is a &lt;b&gt;Cavalry&lt;/b&gt; model then both rider and &lt;b&gt;Mount&lt;/b&gt; will suffer these hits), and if it was a &lt;b&gt;Cavalry&lt;/b&gt; model then it is also Knocked Flying. If it is slain, skip the next step and move straight to step 6.&lt;/li&gt;
+&lt;li&gt;If it survives, place it in base contact with the target model as close to the &lt;b&gt;Monster&lt;/b&gt; as possible. If this is not possible, place the model in base contact with the target as close to the position it should have been in as possible. If there is nowhere to place the model in base contact with the target, move other models the minimum distance to make this possible. The Hurled model is then knocked Prone.&lt;/li&gt;
+&lt;li&gt;The target model is then knocked Prone, if it has a Strength of 5 or less, and will suffer one Strength 6 hit (if it is a &lt;b&gt;Cavalry&lt;/b&gt; model then both rider and &lt;b&gt;Mount&lt;/b&gt; will suffer these hits). If it is a &lt;b&gt;Cavalry&lt;/b&gt; model then it is also Knocked Flying.&lt;/li&gt;
+&lt;li&gt;If there are no enemy models eligible to be the target, then the &lt;b&gt;Monster&lt;/b&gt; may choose a point on the battlefield it can draw Line of Sight within the Hurl Distance instead. Place the Hurled model on the chosen point; it is then knocked Prone and suffers two Strength 6 hits.&lt;/li&gt;
+&lt;li&gt;Once a &lt;b&gt;Monster&lt;/b&gt; model has used a Hurl, the Combat immediately ends and no further Strikes or Brutal Power Attacks can be made. A Monster cannot Hurl in the same turn in which it participates in a Heroic Combat.&lt;/li&gt;
+&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hand-weapon.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hand Weapon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hand-weapon.description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">These are the standard kind of weapon a model may carry, and is anything wielded in a single hand, such as a sword, an axe, a mace or all manner of other weapons. The exact kind of weapon being carried doesn’t matter; all hand weapons function the same. A hand weapon has no specific rules attached to it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">two-handed-weapon.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two-handed Weapons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">two-handed-weapon.description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A two-handed weapon is the kind that requires two hands to wield; as a result, a model wielding a two-handed weapon cannot use any other wargear that would also require the use of a hand (such as a shield) in the same Combat in which they use a two-handed weapon. If the only Melee Weapon a model carries is a two-handed weapon, then they must use it in a Combat – they cannot choose not to.
+When a model fights with a two-handed weapon in a Combat, they suffer a -1 penalty to their Duel Roll. However, if the model rolls a natural 6 for their Duel Roll, they do not suffer this penalty. When a model with a two-handed weapon makes a Strike against an enemy model, they apply a +1 modifier to their ToWound Roll – so a 3 would become a 4, a 4 would become a 5, and so on. In the case of when two rolls are required (such as needing a 6+/4+), this will affect both rolls.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hand-and-a-half-weapon.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hand-and-a-half Weapon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hand-and-a-half-weapon.description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A model armed with a hand-and-a-half weapon canchooseto fight with it as either a hand weapon or a two-handedweapon. When a model with a hand-and-a-half weapontakes part in a Combat, they must decide if they are usingtheir weapon as a hand weapon or a two-handed weaponbefore they make their Duel Roll.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unarmed.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unarmed models</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unarmed.description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Some models don’t carry any weapons at all; such modelsare said to be Unarmed. A model is only ever consideredtobeUnarmed if their profile explicitly states so, or if theystartedthe game with some form of weapon and those weapons have been lost or destroyed during the course of the game. An Unarmed model suffers a -1 penalty to any Duel Roll theymake, and also suffers a -1 penalty to any ToWound Rolls they make when making Strikes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spear.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spear</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">spear</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.description</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">An &lt;b&gt;Infantry&lt;/b&gt; model armed with a spear may assist a friendly model during a Combat, so long as their ally has the same base size or smaller – this is called Supporting.
+If a spear-armed model is not Engaged in Combat, then it can Support a friendly model in base contact. When they do, they contribute a single dice to the Duel Roll of the Combat the model they are Supportingispartof. This dice uses the Supporting model’s own Fight Value, and if they win they will make a single Strike using their own Strength. In a Multiple Combat, a Supporting model doesn’t have to Strike the same model as the model it is Supporting.
+Models that are Supporting do not count as being involved in the Combat they are Supporting. As a result, they cannot be targeted by Strikes, will not be knocked Prone by a Charging &lt;b&gt;Cavalry&lt;/b&gt; model, cannot benefit from a Heroic Combat, and never count as being part of the Combat for the purpose of special rules or determining how many models are taking part on each side.
+A spear-armed model can only Support a single Combat during each Fight Phase. A spear-armed model cannot Support a Combat after already being Engaged in Combat. The only exception to this is that a spear-armed model that is involved in a successful Heroic Combat, and therefore gets to Move, may Move to Support a Combat, provided it hasn’t Supported an other Combat that Fight Phase.
+A model with a spear can use it as a hand weapon when they are Engaged in Combat. A model can’t Support if it is Prone, rendered unable to Activate or has made a Shooting Attack during the same turn.
+A Hero that is Supporting may use Might Points to improve a Duel Roll or To Wound Rolls as normal. However, a Hero that has declared a Heroic Action in the Fight Phase cannot Support during that Fight Phase.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pike.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pike</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.description</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Pikes function in much the same way as spears, and allow models to Support in exactly the same way as those armed with a spear (see &lt;rule id="spear"&gt;spear&lt;/rule&gt;).
+Additionally, a model armed with a pike can Support another friendly model armed with a pike that is Supporting a friendly model Engaged in Combat – essentially giving two Supports to the same model.
+A pike requires two hands to use, and so a model armed with a pike will suffer a -1 penalty to their Duel Rolls if they are armed with a shield or a Missile Weapon.
+As models armed with pikes can effectively Support at three models deep (one Engaged in Combat and two Supporting), it can be very easy to cause your own models to be Trapped, as only one model may Back Away not two. This is the risk of Supporting in such depth.
+Additionally, if a Cavalry model Charges a model armed witha pike, thenthe model with a pike will gain a bonus of +1 ToWound when making Strikes against the &lt;b&gt;Mount&lt;/b&gt; in the ensuing Combat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lance.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lance</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">lance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.description</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A &lt;b&gt;Cavalry&lt;/b&gt; model using a lance applies a +1 modifier on any To Wound Rolls when making Strikes in a Combat in which it Charged. This modifier is not applied if the &lt;b&gt;Cavalry&lt;/b&gt; model Charges whilst within Difficult Terrain.
+If a &lt;b&gt;Cavalry&lt;/b&gt; model Dismounts or loses their &lt;b&gt;Mount&lt;/b&gt;, then they must discard their lance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">war-spear.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">War spear</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">war-spear</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.description</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A war spear follows the rules for a spear when wielded by an &lt;b&gt;Infantry&lt;/b&gt; model, and follows the rules for a lance when wielded by a &lt;b&gt;Cavalry&lt;/b&gt; model. The only exception is that a Cavalry model doesn’t have to discard the war spear when they Dismount or lose their &lt;b&gt;Mount&lt;/b&gt;.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">whip.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whip</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">whip</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.description</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A whip counts as a throwing weapon with a Strengthof 1 and a range of 2". It can also be used as a handweapon in a Combat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">elven-weapon.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elven weapon</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">elven-weapon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.description</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Some weapons will be described as an Elven weapon; for example, a model may have an Elven hand weapon or an Elven two-handed weapon.
+If a model fights with an Elven weapon in a Combat, they will be more likely to win the Duel Roll in the result of a Drawn Combat. In these instances, a Good model armed with an Elven weapon will win the roll-off ona 3+, whilst an Evil model armed with an Elven weapon will win the roll-off on a 1-4. If both sides have an Elven weapon, neither side gains the benefit.
+Some Missile Weapons may also be classed as Elven weapons; however, the above bonus only applies to Melee Weapons as a model cannot choose to fight with a Missile Weapon in a Combat.
+Any weapon with the word ‘Elf’ in its name is automatically considered to be an Elven weapon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">master-forged.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master-forged</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">master-forged</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.description</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Some weapons may be classed as Master-forged. A model using a Master-forged weapon doesn't suffer the -1 penalty to the Duel Roll for using it as a &lt;rule id="two-handed-weapon"&gt;two-handed weapon&lt;/rule&gt;.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">staff-of-power.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff of Power</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">staff-of-power</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.description</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A Staff of Power is a &lt;rule id="hand-and-a-half-weapon"&gt;hand-and-a-half weapon&lt;/rule&gt;. Additionally, the wielder of a Staff of Power gains a free Will Point at the start of each turn. If this free Will Point is not spent by the end of the turn, it is lost.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bow.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bow</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">bow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.description</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">The term bow covers a wide range of Missile Weapons, including bows, longbows, Elf bows, Dwarf bows, and so on – essentially any Missile Weapon with ‘bow’ in its name (with the exception of a &lt;rule id="crossbow"&gt;crossbow&lt;/rule&gt;). All bows function the same; a model can make a Shooting Attack with a bow during the Shoot Phase provided it has not Moved over half its Move Value during the preceding Move Phase.
+The only difference between the various types of bow will be the Strength and range of that particular bow, as shown on the Missile Weapon Chart later on.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">throwing-weapon.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Throwing weapon</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">throwing-weapon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.description</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A model with a throwing weapon can make a Shooting Attack with it in the Shoot Phase, even if it Moved its full Move Value in the preceding Move Phase.
+Alternatively, once per turn, a model may make a Shooting Attack with a throwing weapon during the Move Phaseas it Charges an enemy model. If a model wishes to use a throwing weapon in this manner, then when it Charges it will stop 1" away from the model it wishes to Charge, andthen make a Shooting Attack against the model. If the model using the throwing weapon begins its Move within the Control Zone of an enemy model it wishes to Charge, then it doesn’t need to Move first before throwing the weapon. This is made using all the normal rules for a Shooting Attack, with the exception of that throwing weapons thrown in this manner do not suffer the -1 penalty To Hit for Moving and Shooting.
+If the target is not slain, then the model continues their Charge as normal and must Charge the target of their Shooting Attack. If the target is slain, then the model may continue to Move as normal, and may even Charge a different target if they wish.
+Throwing weapons do not count towards an Army’s Bow Limit. However, an Army can only have one third of its models armed with throwing weapons, unless specifically stated otherwise.
+Throwing spears follow the same rules as throwing weapons, but have a slightly different profile, as shown on the Missile Weapon Chart.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crossbow.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crossbow</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">crossbow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.description</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A model with a crossbow cannot make a Shooting Attack with it in the same turn in which it Moved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blowpipe.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blowpipe</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">blowpipe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.description</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A model with a blowpipe can make a Shooting Attack with it in the Shoot Phase provided it has not Moved over half its Move Value during the preceding Move Phase. Additionally, a blowpipe benefits from the Poisoned Attacks special rule.
+Blowpipes do not count towards an Army’s Bow Limit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sling.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sling</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">sling</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.description</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A model with a sling can make two Shooting Attacks with it in the Shoot Phase, providing they did not Move at all during the preceding Move Phase. If the model Moved up to half their Move Value in the preceding Move Phase, they may make a single Shooting Attack. If they Moved over half their Move Value in the preceding Move Phase, they may not make a Shooting Attack in the Shoot Phase.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">banner.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banner</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">banner</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.description</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A banner has a 3" area of effect that extends out from the model carrying the banner (although some special banners may have a larger range). If a friendly model is within the range of one or more friendly banners, can draw Line of Sight to that banner, and is either Engaged in Combat or Supporting a friendly model, then that Combat is affected by the banner. If a Combat is affected by a banner then a single friendly model in that Combat (including a Supporting model) can re-roll a single dice in the Duel Roll. If a Combat is affected by multiple friendly banners, then this will still only allow a single dice to be re-rolled as part of the Duel Roll, not one for each banner. A model cannot use a banner to re-roll a dice in a Duel Roll that the model is currently winning, in order to try to lose the Combat.
+A banner must be flying in order to inspire its followers. If a model carrying a banner is Prone, then friendly models cannot benefit from it, or any special rules associated with the banner if applicable.
+If a &lt;b&gt;Hero&lt;/b&gt; has a special rule that means that friendly models in a certain range treat them as a banner, then the &lt;b&gt;Hero&lt;/b&gt; must be standing in order for the effect of the banner to be applicable.
+It is possible that one player will use their banner to re-roll a dice and then find themselves winning the Duel Roll, in which case their opponent may wish to use a banner of their own. This is perfectly fine, though each side may still only re-roll a single dice as the result of using a banner or a special rule that counts as a banner.
+If a banner states that it only affects models with certain keywords, then those models must be in range of the banner themselves for the banner to affect that Combat, and only those models may re-roll a dice as a result of the banner.
+A model carrying a banner suffers a -1 penalty to their Duel Rolls.
+If a &lt;b&gt;Warrior&lt;/b&gt; carrying a banner (not a &lt;b&gt;Hero&lt;/b&gt;) is removed from the battlefield as a casualty for any reason (such as being slain or fleeing the board as the result of being part of a Broken Army), then they may pass their banner onto another friendly &lt;b&gt;Warrior&lt;/b&gt; model in base contact. However, they cannot pass their banner onto a model that is Prone, Engaged in Combat or to a model that could not normally take a banner as part of their profile. Swap the models over if they are the same type of &lt;b&gt;Warrior&lt;/b&gt;, or find a suitable model in your collection. When a model takes a banner in this manner, it will count as having the wargear its profile allows it to have when it is upgraded to carry a banner as part of its profile, and will drop all others. So, if a Warrior of Minas Tirith with a spear and shield were to pick up a banner, it would have to drop its shield and spear as a Warrior of Minas Tirith that has a banner does not also have a spear and shield.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">elven-cloak.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elven cloak</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">elven-cloak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.description</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A model wearing an Elven cloak has the Stalk Unseen special rule. Additionally, models targeting an &lt;b&gt;Infantry&lt;/b&gt; model wearing an Elven cloak with a Shooting Attack suffer a -1 penalty when rolling To Hit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">war-drum.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">War drum</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">war-drum</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.description</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A model with a war drum may use it during the Declare Heroic Actions step of each Move Phase to declare a &lt;rule id="heroic-march"&gt;Heroic March&lt;/rule&gt; for free, without spending a Might Point, even if they are not a &lt;b&gt;Hero&lt;/b&gt;. This free Heroic March has the following exceptions:
+&lt;ul&gt;
+&lt;li&gt;A model with a war drum that declares a Heroic March must always shout At the Double.&lt;/li&gt;
+&lt;li&gt;The range of this At the Double is 12" rather than 6".&lt;/li&gt;
+&lt;li&gt;Additionally, friendly models must finish their Activation within 12" rather than 6".&lt;/li&gt;
+&lt;li&gt;The Heroic March declared when a model uses a war drum will only affect friendly models with the same keywords as the ones shown in brackets after the war drum. So if a model has a war drum (&lt;b&gt;Mordor&lt;/b&gt;) then it will only affect models with the &lt;b&gt;Mordor&lt;/b&gt; keyword.&lt;/li&gt;
+&lt;/ul&gt;
+As a war drum allows a model to declare a free Heroic March, models cannot be affected by both a war drum and a normal Heroic March in the same turn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">war-horn.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">War horn</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">war-horn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.description</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Models within 24" of a friendly model with a war horn gain a bonus of +1 to any Courage Tests they take. Additionally, a model with a war horn gains the &lt;rule id="dominant"&gt;Dominant (2)&lt;/rule&gt; special rule and can use it once per game to increase the range of a friendly &lt;b&gt;Hero&lt;/b&gt; model’s Stand Fast by 3", so long as the model with the war horn is in range of the &lt;b&gt;Hero&lt;/b&gt; model’s Stand Fast before this increase. If a &lt;b&gt;Hero&lt;/b&gt; model has a war horn themselves, they may use it to increase the range of their own Stand Fast by 3" instead. A war horn is treated as an Active ability (see page 123).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">armour.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armour</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">armour</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.description</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A model wearing armour will add 1 to their Defence characteristic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">light-armour.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Light armour</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">light-armour</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.description</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A model wearing light armour will add 1 to their Defence characteristic against Shooting Attacks. If a model is wearing light armour then the Defence improvement will not have been added onto their profile.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heavy-armour.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heavy armour</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">heavy-armour</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.description</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A model wearing heavy armour will add 2 to their Defence characteristic.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heavy-dwarf-armour.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heavy Dwarf armour</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">heavy-dwarf-armour</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.description</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A model wearing heavy Dwarf armour will add 3 to their Defence characteristic.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mithril-armour.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mithril armour</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">mithril-armour</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.description</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A model wearing Mithril armour will add 3 to their Defence characteristic. Additionally, &lt;b&gt;Monster&lt;/b&gt; models cannot use the &lt;rule id="rend"&gt;Rend&lt;/rule&gt; Brutal Power Attack against a model wearing Mithril armour.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shield.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shield</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">shield</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.description</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A model carrying a shield adds 1 to their Defence characteristic. Where a model is listed as carrying a shield in its profile, then the improvement in its Defence characteristic will already have been included in their profile.
+A shield is cumbersome, and so a model carrying a shield that wishes to use their &lt;rule id="hand-and-a-half-weapon"&gt;hand-and-a-half weapon&lt;/rule&gt; as a &lt;rule id="two-handed-weapon"&gt;two-handed weapon&lt;/rule&gt; during a Combat cannot gain the Defence bonus for carrying a shield during that Combat. Additionally, a model carrying a shield does not gain the Defence bonus if it also carries a type of bow, crossbow, two-handed weapon or &lt;rule id="pike"&gt;pike&lt;/rule&gt;.
+A model with a shield can also use the Shielding special rule:
+&lt;h3&gt;Shielding&lt;/h3&gt;
+A model carrying a shield may declare they are Shielding at the start of a Combat they are involved in, before the Duel Roll is made. If they do, the Shielding model will double their Attacks characteristic for the duration of the Combat; however, if they win the Duel Roll they cannot make Strikes having put their effort into surviving. They also don’t gain any advantages of the special rules of their weapons (such as if they have an Elven weapon) as they are not using them in the Combat and are using their shield instead.
+In a Multiple Combat, if one model wishes to declare they are Shielding, then all friendly models must do so. If some of them cannot, then no models may declare they are Shielding. Models that are Shielding cannot be Supported.
+&lt;b&gt;Cavalry&lt;/b&gt; models cannot declare they are Shielding. Additionally, Shielding is treated as an Active ability (see page 123).
+A Prone model can declare they are Shielding – infact, it is a sensible way of trying to get them to stand backup as a Prone model can’t make Strikes anyway!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">light-shield.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Light shield</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">light-shield</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.description</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A model with a light shield does not gain a bonus to its Defence. However, it may use the Shielding special rule as described on the &lt;rule id="shield"&gt;Shield&lt;/rule&gt; equipment.</t>
   </si>
 </sst>
 </file>
@@ -1423,7 +2282,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1434,6 +2293,22 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -1457,7 +2332,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B203"/>
+  <dimension ref="A1:B267"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="48.83"/>
@@ -3088,6 +3963,508 @@
       <c r="B203" s="2" t="s">
         <v>405</v>
       </c>
+    </row>
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="242.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="355.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="B210" s="0" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="114.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="299.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A224" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A226" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A227" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A228" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="B228" s="6" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="143.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A233" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A234" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="86.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A235" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A236" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="237" customFormat="false" ht="228.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A238" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A239" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A240" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A241" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A242" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="B243" s="1" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A244" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="412.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A245" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A246" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="247" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A247" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A248" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="249" customFormat="false" ht="157.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A249" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A250" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="72.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A251" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="B251" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A252" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="B252" s="1" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A253" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="B253" s="6" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A254" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="B254" s="1" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="255" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A255" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="B255" s="1" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A256" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="B256" s="1" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A257" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A258" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="B258" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A259" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="B259" s="1" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A260" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="261" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A261" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="B261" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A262" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="263" customFormat="false" ht="327.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A263" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A264" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="265" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A265" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="B265" s="1" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A266" s="4"/>
+    </row>
+    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A267" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3113,10 +4490,10 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
     </row>

--- a/data/raw/rules/translations.xlsx
+++ b/data/raw/rules/translations.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="486">
   <si>
     <t xml:space="preserve">key</t>
   </si>
@@ -38,20 +38,7 @@
     <t xml:space="preserve">ancient-enemies.description</t>
   </si>
   <si>
-    <t xml:space="preserve">A model with this special rule must re-roll To Wound Rolls of a natural 1 when making Strikes against a model with the keywords listed in brackets in that model's profile. So, a model with the Ancient Enemies (Elf) special rule would re-roll To Wound Rolls of a natural 1 against Elf models.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">arcing-shot.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arcing Shot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">arcing-shot.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Siege Engine that Shoots by Arcing Shot does not need Line of Sight to its target, or to a model its shot would scatter on to, so long as another friendly model has Line of Sight to the initial target. After determining the actual target, a Siege Engine with Arcing Shot does not make In The Way Tests for intervening models and terrain (the shot goes over them). However, anything that is clearly taller than the actual target and would be above the actual target when the shot comes down will incur an In The Way Test. This could include the likes of trees, ledges, or rocks that jut out from cliff faces; a degree of common sense will be needed here - a whole tree would provide this In The Way, but a single branch would not!
-This is also the case for when a Siege Engine with Arcing Shot hits a War Beast with a Howdah, as the Howdah is above the War Beast and so will provide an In The Way Test.</t>
+    <t xml:space="preserve">A model with this special rule must re-roll To Wound Rolls of a natural 1 when making Strikes against a model with the keywords listed in brackets in that model's profile. So, a model with the Ancient Enemies (&lt;b&gt;Elf&lt;/b&gt;) special rule would re-roll To Wound Rolls of a natural 1 against &lt;b&gt;Elf&lt;/b&gt; models.</t>
   </si>
   <si>
     <t xml:space="preserve">aura-of-command.name</t>
@@ -111,7 +98,7 @@
     <t xml:space="preserve">bane-weapons.description</t>
   </si>
   <si>
-    <t xml:space="preserve">A Bane Weapon will be presented as Xbane, where X is a specific Race keyword. For each successful Strike caused by a Bane Weapon (i.e., one that causes a Wound that is not prevented), the Bane Weapon will inflict D3 Wounds rather than 1 if the target of the Strike has the same keyword as the Bane Weapon. So, a weapon with the Orcbane special rule will deal D3 Wounds rather than 1 against Orc models.</t>
+    <t xml:space="preserve">A Bane Weapon will be presented as Xbane, where X is a specific Race keyword. For each successful Strike caused by a Bane Weapon (i.e., one that causes a Wound that is not prevented), the Bane Weapon will inflict D3 Wounds rather than 1 if the target of the Strike has the same keyword as the Bane Weapon. So, a weapon with the &lt;b&gt;Orc&lt;/b&gt;bane special rule will deal D3 Wounds rather than 1 against &lt;b&gt;Orc&lt;/b&gt; models.</t>
   </si>
   <si>
     <t xml:space="preserve">banishment.name</t>
@@ -123,7 +110,92 @@
     <t xml:space="preserve">banishment.description</t>
   </si>
   <si>
-    <t xml:space="preserve">This Magical Power targets one enemy Spirit model within range. The target immediately suffers 1 Wound. If this Magical Power targets a Cavalry model, the caster must choose whether the rider or the Mount is the target.</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">This Magical Power targets one enemy &lt;b&gt;Spirit&lt;/b&gt; model within range. The target immediately suffers 1 Wound. If this Magical Power targets a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Cavalry</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;/b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> model, the caster must choose whether the rider or the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Mount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;/b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> is the target.</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">black-dart.name</t>
@@ -135,8 +207,92 @@
     <t xml:space="preserve">black-dart.description</t>
   </si>
   <si>
-    <t xml:space="preserve">A sinister dark force leaps from the caster’s hand, driving itself into the flesh of its victim and towards their heart.
-This Magical Power targets one enemy model within range. The target immediately suffers one Strength 6 hit. If this Magical Power targets a Cavalry model, the caster must choose whether the rider or the Mount is the target.</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">This Magical Power targets one enemy model within range. The target immediately suffers one Strength 6 hit. If this Magical Power targets a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Cavalry</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;/b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> model, the caster must choose whether the rider or the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Mount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;/b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> is the target.</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">blades-of-the-dead.name</t>
@@ -196,7 +352,8 @@
     <t xml:space="preserve">bodyguard.description</t>
   </si>
   <si>
-    <t xml:space="preserve">All models with this special rule in an Army must select a Hero to bodyguard; this will automatically be the General if they have the same Faction keyword as this model. If the General does not have the same Faction keyword as this model, then they will bodyguard the Hero with the highest Heroic Tier amongst those who have the same Faction keyword (if there are multiple of the same Heroic Tier, you may choose which will be bodyguarded). All models of the same type must choose the same Hero to bodyguard. So long as the bodyguarded Hero is alive and on the battlefield, all models who are bodyguarding that Hero will automatically pass all Courage Tests they are required to take.</t>
+    <t xml:space="preserve">All models with this special rule in an Army must select a &lt;b&gt;Hero&lt;/b&gt; to bodyguard; this will automatically be the &lt;b&gt;General&lt;/b&gt; if they have the same Faction keyword as this model. If the &lt;b&gt;General&lt;/b&gt; does not have the same Faction keyword as this model, then they will bodyguard the &lt;b&gt;Hero&lt;/b&gt; with the highest Heroic Tier amongst those who have the same Faction keyword (if there are multiple of the same Heroic Tier, you may choose which will be bodyguarded). All models of the same type must choose the same &lt;b&gt;Hero&lt;/b&gt; to bodyguard.
+So long as the bodyguarded &lt;b&gt;Hero&lt;/b&gt; is alive and on the battlefield, all models who are bodyguarding that &lt;b&gt;Hero&lt;/b&gt; will automatically pass all Courage Tests they are required to take.</t>
   </si>
   <si>
     <t xml:space="preserve">burly.name</t>
@@ -232,7 +389,7 @@
     <t xml:space="preserve">cave-dweller.description</t>
   </si>
   <si>
-    <t xml:space="preserve">A model with this special rule applies a +1 modifier to any Jump, Leap and Climb Tests they take. Additionally, a model with this special rule suffers no penalties to how far they can see when fighting in the dark.</t>
+    <t xml:space="preserve">A model with this special rule applies a +1 modifier to any Jump, Leap and Climb Tests they take. Additionally, a model with this special rule suffers no penalties to how far they can see when fighting in the dark. &lt;u&gt;This special rule may be used by models that are not yet on the battlefield.&lt;/u&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">chill-soul.name</t>
@@ -244,7 +401,92 @@
     <t xml:space="preserve">chill-soul.description</t>
   </si>
   <si>
-    <t xml:space="preserve">This Magical Power targets one enemy model in range. The target immediately suffers 1 Wound. If this Magical Power targets a Cavalry model, the caster must choose whether the rider or the Mount is the target.</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">This Magical Power targets one enemy model in range. The target immediately suffers 1 Wound. If this Magical Power targets a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Cavalry</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;/b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> model, the caster must choose whether the rider or the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Mount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;/b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> is the target.</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">collapse-rocks.name</t>
@@ -280,20 +522,92 @@
     <t xml:space="preserve">curse.description</t>
   </si>
   <si>
-    <t xml:space="preserve">This Magical Power targets one enemy model in range. The target immediately loses 1 Fate Point. If this Magical Power targets a Cavalry model, the caster must choose whether the rider or the Mount is the target.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">direct-shot.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct Shot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">direct-shot.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Siege Engine that Shoots by Direct Shot will need Line of Sight to the initial target. Additionally, if the shot scatters onto another target, the Siege Engine will need to have Line of Sight to this target in order for them to be selected as the actual target. In both of these instances, this Line of Sight is drawn from the firing point of the Siege Engine, so the tip of a ballista or siege bow for example.
-After determining the actual target, a Siege Engine with Direct Shot will make In The Way Tests in the same way as any other Shooting Attack.</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">This Magical Power targets one enemy model in range. The target immediately loses 1 Fate Point. If this Magical Power targets a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Cavalry</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;/b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> model, the caster must choose whether the rider or the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Mount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;/b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> is the target.</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">dominant.name</t>
@@ -305,7 +619,8 @@
     <t xml:space="preserve">dominant.description</t>
   </si>
   <si>
-    <t xml:space="preserve">This model counts as the number of models as shown in brackets when working out how many models are in range of an objective, in a specific area of the board, or when working out how many models have escaped the battlefield. So, a model with Dominant (3) would count as three models in range of an objective, or in a specific area of the board, or three models when working out how many models have escaped the battlefield. If a model would gain this special rule whilst in range of another model or specific area of the board, and then Moves off the board, they will not gain the benefit of this special rule once off the board.</t>
+    <t xml:space="preserve">This model counts as the number of models as shown in brackets when working out how many models are in range of an objective, in a specific area of the board, or when working out how many models have escaped the battlefield. So, a model with Dominant (3) would count as three models in range of an objective, or in a specific area of the board, or three models when working out how many models have escaped the battlefield.
+If a model would gain this special rule whilst in range of another model or specific area of the board, and then Moves off the board, they will not gain the benefit of this special rule once off the board.</t>
   </si>
   <si>
     <t xml:space="preserve">drain-courage.name</t>
@@ -317,7 +632,92 @@
     <t xml:space="preserve">drain-courage.description</t>
   </si>
   <si>
-    <t xml:space="preserve">This Magical Power targets one enemy model in range. The target immediately worsens their Courage value by 1 for the remainder of the game; so a model with a Courage of 5+ that is affected by this Magical Power would then have a Courage of 6+. A model can be affected by this Magical Power multiple times over the course of the battle, worsening its Courage value each time. If this Magical Power targets a Cavalry model, the caster must choose whether the rider or the Mount is the target.</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">This Magical Power targets one enemy model in range. The target immediately worsens their Courage value by 1 for the remainder of the game; so a model with a Courage of 5+ that is affected by this Magical Power would then have a Courage of 6+. A model can be affected by this Magical Power multiple times over the course of the battle, worsening its Courage value each time. If this Magical Power targets a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Cavalry</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;/b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> model, the caster must choose whether the rider or the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Mount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;/b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> is the target.</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">enchant-blades.name</t>
@@ -341,7 +741,54 @@
     <t xml:space="preserve">enrage-beast.description</t>
   </si>
   <si>
-    <t xml:space="preserve">This Magical Power targets one friendly Beast model within range. The target increases its Fight Value, Strength and Attacks by 2, and gains the Fearless special rule, until the End Phase of the turn, at which point the target will immediately suffer 1 Wound.</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">This Magical Power targets one friendly </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Beast</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;/b&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">model within range. The target increases its Fight Value, Strength and Attacks by 2, and gains the Fearless special rule, until the End Phase of the turn, at which point the target will immediately suffer 1 Wound.</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">expert-rider.name</t>
@@ -401,7 +848,7 @@
     <t xml:space="preserve">fell-sight.description</t>
   </si>
   <si>
-    <t xml:space="preserve">A model with this special rule does not need to have Line of Sight to be able to Charge an enemy model. Additionally, a model with this special rule can Charge or target an enemy model with the Stalk Unseen special rule with no penalty. If a Mount has this special rule, the rider may benefit from it whilst they remain mounted.</t>
+    <t xml:space="preserve">A model with this special rule does not need to have Line of Sight to be able to Charge an enemy model. Additionally, a model with this special rule can Charge or target an enemy model with the &lt;rule id="stalk-unseen"&gt;Stalk Unseen&lt;/rule&gt; special rule with no penalty. If a &lt;b&gt;Mount&lt;/b&gt; has this special rule, the rider may benefit from it whilst they remain mounted.</t>
   </si>
   <si>
     <t xml:space="preserve">flameburst.name</t>
@@ -416,18 +863,6 @@
     <t xml:space="preserve">This Magical Power targets one enemy model in range. The target immediately suffers one Strength 6 hit. This is a fire-based attack, so if a model is immune to fire-based attacks, they are immune to this Magical Power.</t>
   </si>
   <si>
-    <t xml:space="preserve">flaming-ammunition.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flaming Ammunition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flaming-ammunition.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Siege Engine upgrade with Flaming Ammunition may re-roll any failed To Wound rolls against a Siege Target.</t>
-  </si>
-  <si>
     <t xml:space="preserve">fly.name</t>
   </si>
   <si>
@@ -437,11 +872,10 @@
     <t xml:space="preserve">fly.description</t>
   </si>
   <si>
-    <t xml:space="preserve">A model with this special rule ignores intervening models and terrain when it Moves – flying over buildings, woods and so on, and ignoring the vertical distance as they Move.
-A model that Moves in this way cannot end its Move overlapping another model, within a piece of woodland terrain, or upon any surface in which it cannot balance safely (flat rock and hills are fine, but don’t try perching a model upon a sloped roof for example). Additionally, a model that Moves in this way cannot finish its Move atop a piece of terrain which it is impossible for the enemy to reach, such as at the top of a sheer rock face with no way up, or straddling one or more pieces of terrain that would allow other models to Move underneath.
+    <t xml:space="preserve">A model with this special rule ignores intervening models and terrain when it Moves – flying over buildings, woods and so on, and ignoring the vertical distance as they Move. A model that Moves in this way cannot end its Move overlapping another model, within a piece of woodland terrain, or upon any surface in which it cannot balance safely (flat rock and hills are fine, but don’t try perching a model upon a sloped roof for example). Additionally, a model that Moves in this way cannot finish its Move atop a piece of terrain which it is impossible for the enemy to reach, such as at the top of a sheer rock face with no way up, or straddling one or more pieces of terrain that would allow other models to Move underneath.
 If a model wishes to do something part way through its Move whilst it is Flying (such as Cast a Magical Power), then it must land in order to do so. When a model lands, there cannot be any models underneath it, and if it lands in an enemy model’s Control Zone then it must Charge that enemy model.
 A model with this special rule can choose not to Fly, and in which case will treat its Move Value as 4” rather than that listed in its profile (usually 12”). If it does, then it gains none of the benefits of the Fly special rule, though it may enter a piece of woodland terrain; however, if it enters a piece of woodland terrain, it cannot elect to Fly again until it has completely left the woods.
-A model that chooses to Fly will ignore enemy Control Zones as it Moves. A model that wishes to Charge when it is flying can Charge any model whose Control Zone it finishes its Move in. If a Flying model wishes to Charge a model that is already Engaged in Combat (or has otherwise lost their Control Zone) then it can only do so if it can land in a position where is is not within the Control Zones of other enemy models.</t>
+A model that chooses to Fly will ignore enemy Control Zones as it Moves. A model that wishes to Charge when it is flying can Charge any model whose Control Zone it finishes its Move in. If a Flying model wishes to Charge a model that is already Engaged in Combat (or has otherwise lost their Control Zone) then it can only do so if it can land in a position where is is not within the Control Zones of other enemy models. &lt;u&gt;This special rule may be used by models that are not yet on the battlefield.&lt;/u&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">fog-of-disarray.name</t>
@@ -480,18 +914,6 @@
     <t xml:space="preserve">This Magical Power targets one friendly model within range. Each time the target becomes the target of a Magical Power Cast by an enemy model, they gain an additional free dice to try to Resist. This free dice can still be rolled even if the target has no Will Points or chooses not to use any from their store.</t>
   </si>
   <si>
-    <t xml:space="preserve">foul-temperament.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foul Temperament</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foul-temperament.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Mumak has 4 Attacks, but suffers a -1 penalty to its Courage Tests when seeing if it will Stampede.</t>
-  </si>
-  <si>
     <t xml:space="preserve">fury.name</t>
   </si>
   <si>
@@ -513,19 +935,7 @@
     <t xml:space="preserve">general-hunter.description</t>
   </si>
   <si>
-    <t xml:space="preserve">If this model slays the enemy General in a Combat, they immediately regain a single point of Might spent earlier in the battle.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gnarled-hide.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gnarled Hide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gnarled-hide.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Mumak has a Defence of 8 rather than 7.</t>
+    <t xml:space="preserve">If this model slays the enemy &lt;b&gt;General&lt;/b&gt; in a Combat, they immediately regain a single point of Might spent earlier in the battle.</t>
   </si>
   <si>
     <t xml:space="preserve">harbinger-of-evil.name</t>
@@ -549,7 +959,7 @@
     <t xml:space="preserve">hatred.description</t>
   </si>
   <si>
-    <t xml:space="preserve">A model with this special rule gains a bonus of +1 To Wound when making Strikes against a model with the same keyword as the one shown in brackets. So, a model with the Hatred (Man) special rule would gain a bonus of +1 To Wound when making Strikes against Man models.</t>
+    <t xml:space="preserve">A model with this special rule gains a bonus of +1 To Wound when making Strikes against a model with the same keyword as the one shown in brackets. So, a model with the Hatred (&lt;b&gt;Man&lt;/b&gt;) special rule would gain a bonus of +1 To Wound when making Strikes against &lt;b&gt;Man&lt;/b&gt; models.</t>
   </si>
   <si>
     <t xml:space="preserve">heroic-accuracy.name</t>
@@ -650,59 +1060,13 @@
     <t xml:space="preserve">heroic-move.description</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A Heroic Move enables a Hero to Activate before other models – essentially defying the usual Priority system. The Hero can then Activate exactly as normal and do anything they would normally be able to do when they Activate. The Hero cannot then be Activated again later in the Move Phase.
+    <t xml:space="preserve">A Heroic Move enables a Hero to Activate before other models – essentially defying the usual Priority system. The Hero can then Activate exactly as normal and do anything they would normally be able to do when they Activate. The Hero cannot then be Activated again later in the Move Phase.
 This Heroic Action can prove extremely valuable, and often when the player without Priority declares a Heroic Move their opponent will also declare one in order to try to keep the initiative.
 If a Hero who has declared a Heroic Move is Charged and Engaged in Combat, or rendered unable to Activate in some other way, then their Heroic Move is cancelled and the Might Point spent is lost.
 &lt;b&gt;With Me&lt;/b&gt; - A Hero who is performing a Heroic Move may choose to shout "With Me" as soon as they are Activated. If they do, note their starting position before they Activate. All friendly models within 6" of the Hero when they shout With Me are automatically affected, and after the Hero has finished their Activation, they must choose to do one of two things:
 &lt;ul&gt;
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;li&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Activate as normal in an order chosen by their controlling player. Any model that Activates as part of a With Me must finish their Activation within 6" of the Hero that shouted With Me. If the model attempts to finish their Activation within 6" of the Hero, but fails a roll (such as a Courage Test, Jump Test or Climb Test) that makes this impossible, they simply stop where they are.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;/li&gt;
-&lt;li&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Forego their Activation, in which case they do not Activate and cannot do so later in the Move Phase. A model that cannot finish its Activation within 6" of the Hero that shouted With Me must choose this option.&lt;/li&gt;
+&lt;li&gt;Activate as normal in an order chosen by their controlling player. Any model that Activates as part of a With Me must finish their Activation within 6" of the Hero that shouted With Me. If the model attempts to finish their Activation within 6" of the Hero, but fails a roll (such as a Courage Test, Jump Test or Climb Test) that makes this impossible, they simply stop where they are.&lt;/li&gt;
+&lt;li&gt;Forego their Activation, in which case they do not Activate and cannot do so later in the Move Phase. A model that cannot finish its Activation within 6" of the Hero that shouted With Me must choose this option.&lt;/li&gt;
 &lt;/ul&gt;
 In either case, the affected models cannot be Activated again later in the Move Phase for any reason.
 A Hero that shouts With Me doesn't have to Move as part of their Activation, and as With Me is shouted at the start of their Activation, if anything would render them unable to Move as part of their Activation (such as failing a Courage Test to Charge an enemy with the Terror special rule) then they will still shout With Me. However, should the Hero be removed as a casualty for any reason (such as fleeing or suffering Falling Damage) then their Heroic Move and With Me will immediately be cancelled.
@@ -712,7 +1076,6 @@
 &lt;li&gt;Forego their Activation, in which case they do not Activate later in the Move Phase and their Heroic Move will be cancelled.&lt;/li&gt;
 &lt;/ul&gt;
 If a Hero who shouted With Me Moves off the board, then any friendly models who are affected by their With Me may also Move off the board if able; however, if they cannot then they must choose to forego their Activation. If a model is affected by a Hero model's With Me, then they can only Move off the board if that Hero also does so.</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">heroic-resolve.name</t>
@@ -776,7 +1139,7 @@
     <t xml:space="preserve">horse-lord.description</t>
   </si>
   <si>
-    <t xml:space="preserve">Whenever the Mount of a model with this special rule suffers a Wound, roll a D6 on a natural 6, the Wound is ignored. Additionally, a model with this special rule can use their own Fate Points to prevent Wounds inflicted upon their Mount.</t>
+    <t xml:space="preserve">Whenever the &lt;b&gt;Mount&lt;/b&gt; of a model with this special rule suffers a Wound, roll a D6 on a natural 6, the Wound is ignored. Additionally, a model with this special rule can use their own Fate Points to prevent Wounds inflicted upon their &lt;b&gt;Mount&lt;/b&gt;.</t>
   </si>
   <si>
     <t xml:space="preserve">instill-fear.name</t>
@@ -788,7 +1151,7 @@
     <t xml:space="preserve">instill-fear.description</t>
   </si>
   <si>
-    <t xml:space="preserve">This Magical Power targets the caster. Enemy models within 6" of the caster are considered to have the Fearful special rule.</t>
+    <t xml:space="preserve">This Magical Power targets the caster. Enemy models within 6" of the caster are considered to have the &lt;rule id="fearful"&gt;Fearful&lt;/rule&gt; special rule.</t>
   </si>
   <si>
     <t xml:space="preserve">invisible.name</t>
@@ -817,7 +1180,7 @@
     <t xml:space="preserve">large-target.description</t>
   </si>
   <si>
-    <t xml:space="preserve">When a model makes a Shooting Attack that targets a model with this special rule, when they are determining models that are In The Way, they ignore models (both friendly and enemy) that do not have any of the following keywords: Monster, Siege Engine, War Beast. If the target model is Engaged in Combat, then the In The Way test for Shooting into Combat is still applied regardless of the model the target model is Engaged in Combat with.</t>
+    <t xml:space="preserve">When a model makes a Shooting Attack that targets a model with this special rule, when they are determining models that are In The Way, they ignore models (both friendly and enemy) that do not have any of the following keywords: &lt;b&gt;Monster&lt;/b&gt;, &lt;b&gt;Siege Engine&lt;/b&gt;, &lt;b&gt;War Beast&lt;/b&gt;. If the target model is Engaged in Combat, then the In The Way test for Shooting into Combat is still applied regardless of the model the target model is Engaged in Combat with.</t>
   </si>
   <si>
     <t xml:space="preserve">leader.name</t>
@@ -829,7 +1192,7 @@
     <t xml:space="preserve">leader.description</t>
   </si>
   <si>
-    <t xml:space="preserve">A model with this special rule can include Warrior models of the type listed in brackets in their Warband.</t>
+    <t xml:space="preserve">A model with this special rule can include &lt;b&gt;Warrior&lt;/b&gt; models of the type listed in brackets in their Warband.</t>
   </si>
   <si>
     <t xml:space="preserve">master-of-battle.name</t>
@@ -841,7 +1204,7 @@
     <t xml:space="preserve">master-of-battle.description</t>
   </si>
   <si>
-    <t xml:space="preserve">Whenever an enemy Hero declares a Heroic Action within 6" of this model, this model may roll a D6. If the result on the dice equals or beats the number shown in brackets, then this model may immediately declare a Heroic Action of the same type without spending a Might Point. This may still be done if this model has no Might Points remaining, or would not normally be able to declare that Heroic Action. If the roll is failed, this model may still declare a Heroic Action if they wish (though not one they cannot usually declare), for the usual cost of a Might Point.</t>
+    <t xml:space="preserve">Whenever an enemy &lt;b&gt;Hero&lt;/b&gt; declares a Heroic Action within 6" of this model, this model may roll a D6. If the result on the dice equals or beats the number shown in brackets, then this model may immediately declare a Heroic Action of the same type without spending a Might Point. This may still be done if this model has no Might Points remaining, or would not normally be able to declare that Heroic Action. If the roll is failed, this model may still declare a Heroic Action if they wish (though not one they cannot usually declare), for the usual cost of a Might Point.</t>
   </si>
   <si>
     <t xml:space="preserve">mighty-blow.name</t>
@@ -877,7 +1240,7 @@
     <t xml:space="preserve">monstrous-charge.description</t>
   </si>
   <si>
-    <t xml:space="preserve">If a model with this special rule Charges into Combat, then it will increase its Attacks characteristic by 1 during the ensuing Fight Phase. Additionally, if this model Charges and subsequently wins the Duel Roll, then all enemy models involved in the Combat with a Strength characteristic lower than this model, will be immediately knocked Prone before this model makes Strikes. Cavalry models will automatically count as suffering the Knocked Flying result on the Thrown Rider Chart.</t>
+    <t xml:space="preserve">If a model with this special rule Charges into Combat, then it will increase its Attacks characteristic by 1 during the ensuing Fight Phase. Additionally, if this model Charges and subsequently wins the Duel Roll, then all enemy models involved in the Combat with a Strength characteristic lower than this model, will be immediately knocked Prone before this model makes Strikes. &lt;b&gt;Cavalry&lt;/b&gt; models will automatically count as suffering the Knocked Flying result on the Thrown Rider Chart.</t>
   </si>
   <si>
     <t xml:space="preserve">mountain-dweller.name</t>
@@ -889,7 +1252,8 @@
     <t xml:space="preserve">mountain-dweller.description</t>
   </si>
   <si>
-    <t xml:space="preserve">A model with this special rule may Move through areas of rocky terrain that are classed as Difficult Terrain as if they are Open Ground. If a Cavalry model has this special rule, but their Mount does not, then this rule does not apply to the Mount. If a Mount has this special rule, then they will still retain their Cavalry Charge bonuses when they Charge, even if the rider does not have this special rule. Additionally, a model with this special rule may re-roll any Jump, Leap, or Climb Tests.</t>
+    <t xml:space="preserve">A model with this special rule may Move through areas of rocky terrain that are classed as Difficult Terrain as if they are Open Ground. If a &lt;b&gt;Cavalry&lt;/b&gt; model has this special rule, but their &lt;b&gt;Mount&lt;/b&gt; does not, then this rule does not apply to the &lt;b&gt;Mount&lt;/b&gt;. If a &lt;b&gt;Mount&lt;/b&gt; has this special rule, then they will still retain their Cavalry Charge bonuses when they Charge, even if the rider does not have this special rule. 
+Additionally, a model with this special rule may re-roll any Jump, Leap, or Climb Tests. &lt;u&gt;This special rule may be used by models that are not yet on the battlefield.&lt;/u&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">natures-wrath.name</t>
@@ -901,7 +1265,54 @@
     <t xml:space="preserve">natures-wrath.description</t>
   </si>
   <si>
-    <t xml:space="preserve">This Magical Power targets all enemy models within range, even if they are not in Line of Sight of the caster. All targets models are immediately knocked Prone. Cavalry models are automatically treated as suffering a Knocked Flying result on the Thrown Rider Chart.</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">This Magical Power targets all enemy models within range, even if they are not in Line of Sight of the caster. All targets models are immediately knocked Prone. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Cavalry</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;/b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> models are automatically treated as suffering a Knocked Flying result on the Thrown Rider Chart.</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">panic-steed.name</t>
@@ -913,7 +1324,92 @@
     <t xml:space="preserve">panic-steed.description</t>
   </si>
   <si>
-    <t xml:space="preserve">This Magical Power targets one enemy Cavalry model within range. The rider is thrown and the Mount immediately flees and is removed as a casualty. The rider is automatically treated as suffering a Knocked Flying result on the Thrown Rider Chart.</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">This Magical Power targets one enemy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Cavalry</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;/b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> model within range. The rider is thrown and the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Mount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;/b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> immediately flees and is removed as a casualty. The rider is automatically treated as suffering a Knocked Flying result on the Thrown Rider Chart.</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">paralyse.name</t>
@@ -939,7 +1435,8 @@
     <t xml:space="preserve">poisoned-attacks.description</t>
   </si>
   <si>
-    <t xml:space="preserve">A model with this special rule must re-roll any To Wound Rolls of a natural 1 when making Shooting Attacks or making Strikes. Sometimes, a particular weapon will be described as benefiting from this special rule. When this is the case, only To Wound Rolls made for that weapon will be able to re-roll To Wound Rolls of a natural 1.</t>
+    <t xml:space="preserve">A model with this special rule must re-roll any To Wound Rolls of a natural 1 when making Shooting Attacks or making Strikes. 
+Sometimes, a particular weapon will be described as benefiting from this special rule. When this is the case, only To Wound Rolls made for that weapon will be able to re-roll To Wound Rolls of a natural 1.</t>
   </si>
   <si>
     <t xml:space="preserve">protection-of-the-valar.name</t>
@@ -954,18 +1451,6 @@
     <t xml:space="preserve">This Magical Power targets one friendly model within range. The target cannot be chosen as the target of enemy Magical Powers or enemy special rules that specifically target a  model. Additionally, enemy models that target the protected model will suffer a -1 penalty to their To Hit roll.</t>
   </si>
   <si>
-    <t xml:space="preserve">rappelling-lines.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rappelling Lines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rappelling-lines.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Models in the Howdah may attempt to dismount during their Activation by rolling a D6. On a 2+, the model dismounts and is placed in base contact with the Mumak. However, on a 1 the model suffers Falling Damage - if it survives, place it in base contact with the Mumak. A model that        successfully dismounts may then continue its  Activation as normal, even Charging if it    wishes, though may not make a shooting    attack that turn.</t>
-  </si>
-  <si>
     <t xml:space="preserve">renew.name</t>
   </si>
   <si>
@@ -975,7 +1460,92 @@
     <t xml:space="preserve">renew.description</t>
   </si>
   <si>
-    <t xml:space="preserve">This Magical Power targets one friendly model in range. The target immediately regains 1 Wound lost earlier in the battle. If this Magical Power targets a Cavalry model, the caster must choose whether the rider or the Mount is the target.</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">This Magical Power targets one friendly model in range. The target immediately regains 1 Wound lost earlier in the battle. If this Magical Power targets a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Cavalry</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;/b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> model, the caster must choose whether the rider or the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Mount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;/b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> is the target.</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">resistant-to-magic.name</t>
@@ -990,18 +1560,6 @@
     <t xml:space="preserve">Every time this model is targeted by a Magical Power, they gain an additional free dice when making a Resist Test, even if they have no Will Points remaining or decide not to use any Will Points. This is cumulative with other rules that confer a similar effect.</t>
   </si>
   <si>
-    <t xml:space="preserve">rocks.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rocks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rocks.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If they do not Move in their Activation, models in the Howdah can make a shooting attack with range 8" and Strength 6 instead of using a different shooting attack.</t>
-  </si>
-  <si>
     <t xml:space="preserve">set-ablaze.name</t>
   </si>
   <si>
@@ -1011,19 +1569,9 @@
     <t xml:space="preserve">set-ablaze.description</t>
   </si>
   <si>
-    <t xml:space="preserve">A model can be Set Ablaze through a number of means. During the End Phase of a turn, any model that is Set Ablaze will immediately suffer one Strength 5 hit. A model that is Set Ablaze can extinguish the flames either by Lying Down and Crawling 1", or by entering a water feature. If either of these things happen, the model is no longer considered to be Set Ablaze. If a model is immune to fire-based attacks, they cannot be Set Ablaze under any circumstances.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">severed-heads.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Severed Heads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">severed-heads.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If a Mordor War Catapult chooses to fire Severed Heads, determine the actual target as normal. Then, instead of rolling To Wound, the actual target and any enemy models within 3" of them must each take a Courage test. If the test is failed, the model flees and is removed as a casualty.</t>
+    <t xml:space="preserve">A model can be Set Ablaze through a number of means. During the End Phase of a turn, any model that is Set Ablaze will immediately suffer one Strength 5 hit. 
+A model that is Set Ablaze can extinguish the flames either by Lying Down and Crawling 1", or by entering a water feature. If either of these things happen, the model is no longer considered to be Set Ablaze. 
+If a model is immune to fire-based attacks, they cannot be Set Ablaze under any circumstances.</t>
   </si>
   <si>
     <t xml:space="preserve">sharpshooter.name</t>
@@ -1035,7 +1583,7 @@
     <t xml:space="preserve">sharpshooter.description</t>
   </si>
   <si>
-    <t xml:space="preserve">When a model with this special rule makes a Shooting Attack that targets a Cavalry model, it may choose either the rider or the Mount as its target. Additionally, if a model with this special rule hits a Cavalry model that it targeted with a Shooting Attack, it does not need to make the In The Way Test to see which part of the model it hits - it will automatically hit the part of the model it targeted, either rider or Mount.</t>
+    <t xml:space="preserve">When a model with this special rule makes a Shooting Attack that targets a &lt;b&gt;Cavalry&lt;/b&gt; model, it may choose either the rider or the &lt;b&gt;Mount&lt;/b&gt; as its target. Additionally, if a model with this special rule hits a &lt;b&gt;Cavalry&lt;/b&gt; model that it targeted with a Shooting Attack, it does not need to make the In The Way Test to see which part of the model it hits - it will automatically hit the part of the model it targeted, either rider or &lt;b&gt;Mount&lt;/b&gt;.</t>
   </si>
   <si>
     <t xml:space="preserve">shieldwall.name</t>
@@ -1048,19 +1596,7 @@
   </si>
   <si>
     <t xml:space="preserve">If this model is carrying a shield, then whilst it is in base contact with two or more other friendly models who also have this special rule and are carrying a shield, then this model receives an additional +1 bonus to its Defence. In Combat, this bonus is calculated before the model Backs Away.
-Models that are Prone or have the Cavalry keyword cannot benefit from, or provide an ally with the benefit from, this special rule.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sigils-of-defiance.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sigils of Defiance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sigils-of-defiance.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Mumak and any models in the Howdah gain the     Resistant to Magic, and whenever they suffer a Wound they may roll a D6. On a natural 6, the Wound is prevented.</t>
+Models that are Prone or have the &lt;b&gt;Cavalry&lt;/b&gt; keyword cannot benefit from, or provide an ally with the benefit from, this special rule.</t>
   </si>
   <si>
     <t xml:space="preserve">sorcerous-blast.name</t>
@@ -1072,8 +1608,55 @@
     <t xml:space="preserve">sorcerous-blast.description</t>
   </si>
   <si>
-    <t xml:space="preserve">This Magical Power targets one enemy model in range. The target immediately suffers one Strength 5 hit. If they survive, they are immediately knocked Prone. If the target was a Cavalry model, they will automatically count as suffering the Knocked Flying result on the Thrown Rider Chart.
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">This Magical Power targets one enemy model in range. The target immediately suffers one Strength 5 hit. If they survive, they are immediately knocked Prone. If the target was a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Cavalry</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;/b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> model, they will automatically count as suffering the Knocked Flying result on the Thrown Rider Chart.
 If the target was Engaged in Combat, then any other model that's also Engaged in the same Combat will also be knocked Prone if it has a Strength of 5 or lower - make sure to Pair Off Combats before working out which models are knocked Prone in this manner.</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">spectral-walk.name</t>
@@ -1085,7 +1668,7 @@
     <t xml:space="preserve">spectral-walk.description</t>
   </si>
   <si>
-    <t xml:space="preserve">A model with this special rule is never slowed by Difficult Terrain. Additionally, a model with this special rule always counts as rolling a 6 for any Climb, Jump, Leap or Swim Tests.</t>
+    <t xml:space="preserve">A model with this special rule is never slowed by Difficult Terrain. Additionally, a model with this special rule always counts as rolling a 6 for any Climb, Jump, Leap or Swim Tests. &lt;u&gt;This special rule may be used by models that are not yet on the battlefield.&lt;/u&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">stalk-unseen.name</t>
@@ -1097,19 +1680,7 @@
     <t xml:space="preserve">stalk-unseen.description</t>
   </si>
   <si>
-    <t xml:space="preserve">An Infantry model with this special rule that is partially concealed from view by a piece of terrain cannot be seen at distances of more than 6". This means that enemy Models cannot target this model with Shooting Attacks, Magical Powers, special rules, or anything else that requires Line of Sight unless they have a completely clear view of this model.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">static.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Static</t>
-  </si>
-  <si>
-    <t xml:space="preserve">static.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If a Siege Engine has the Static special rule, then it can be Moved or rotated.</t>
+    <t xml:space="preserve">An &lt;b&gt;Infantry&lt;/b&gt; model with this special rule that is partially concealed from view by a piece of terrain cannot be seen at distances of more than 6". This means that enemy Models cannot target this model with Shooting Attacks, Magical Powers, special rules, or anything else that requires Line of Sight unless they have a completely clear view of this model.</t>
   </si>
   <si>
     <t xml:space="preserve">strengthen-will.name</t>
@@ -1121,7 +1692,92 @@
     <t xml:space="preserve">strengthen-will.description</t>
   </si>
   <si>
-    <t xml:space="preserve">This Magical Power targets one friendly model within range. The target immediately regains a single Will Point spent earlier in the battle. If this Magical Power targets a Cavalry model, the caster must choose whether the rider or the Mount is the target.</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">This Magical Power targets one friendly model within range. The target immediately regains a single Will Point spent earlier in the battle. If this Magical Power targets a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Cavalry</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;/b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> model, the caster must choose whether the rider or the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Mount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;/b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> is the target.</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">survival-instinct.name</t>
@@ -1145,7 +1801,8 @@
     <t xml:space="preserve">swift-movement.description</t>
   </si>
   <si>
-    <t xml:space="preserve">A model with this special rule is never slowed by Difficult Terrain, with the exception of water features. It can also ignore Obstacles as it Moves, allowing it to Move at any angle without having to make a Climb or Jump Test, though it will still count any vertical distance it has Moved towards its Move Value. A model with this special rule must finish its Move as flat to the playing surface as possible - no models finishing upside down, halfway up a wall, or at an angle, for example!</t>
+    <t xml:space="preserve">A model with this special rule is never slowed by Difficult Terrain, with the exception of water features. It can also ignore Obstacles as it Moves, allowing it to Move at any angle without having to make a Climb or Jump Test, though it will still count any vertical distance it has Moved towards its Move Value. 
+A model with this special rule must finish its Move as flat to the playing surface as possible - no models finishing upside down, halfway up a wall, or at an angle, for example! &lt;u&gt;This special rule may be used by models that are not yet on the battlefield.&lt;/u&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">sworn-protector.name</t>
@@ -1183,7 +1840,7 @@
   <si>
     <t xml:space="preserve">If a model wishes to Charge a model with this special rule, then it must take a Courage Test at the start of its Move. If the test is passed, the model may Charge as normal. If the test is failed, the model cannot Move that turn, but may otherwise act normally.
 Sometimes a situation may open up the chance for a model to Charge a model with Terror part way through their Move, such as moving a different model with magic or killing something in the way with a throwing weapon. In such instances, the model only needs to take the Courage Test at the point in which the Terror causing model becomes possible to Charge. If a model making a Jump, Climb or Leap Test finishes within the Control Zone of an enemy with Terror and would normally be able to Charge, they will take their Courage Test after they have made their Jump, Climb or Leap Test.
-Sometimes, a model may only cause Terror in certain enemies. In these instances, a keyword will follow Terror in brackets, and only models with that keyword will need to take a Courage Test to Charge the model. So, a model with Terror (Orc) will only cause Terror in Orc models.</t>
+Sometimes, a model may only cause Terror in certain enemies. In these instances, a keyword will follow Terror in brackets, and only models with that keyword will need to take a Courage Test to Charge the model. So, a model with Terror (&lt;b&gt;Orc&lt;/b&gt;) will only cause Terror in &lt;b&gt;Orc&lt;/b&gt; models.</t>
   </si>
   <si>
     <t xml:space="preserve">throw-stones.name</t>
@@ -1207,7 +1864,7 @@
     <t xml:space="preserve">timid.description</t>
   </si>
   <si>
-    <t xml:space="preserve">If a Mount has this special rule, then every time it wishes to Charge an enemy model it must take a Courage Test. It may use its rider's Courage Value, but may never benefit from special rules or Magical Powers that would allow it to automatically pass a Courage Test. If the test is failed, the model cannot Move that turn but may otherwise act normally. A model with this special rule gains no Cavalry Charge bonuses.</t>
+    <t xml:space="preserve">If a &lt;b&gt;Mount&lt;/b&gt; has this special rule, then every time it wishes to Charge an enemy model it must take a Courage Test. It may use its rider's Courage Value, but may never benefit from special rules or Magical Powers that would allow it to automatically pass a Courage Test. If the test is failed, the model cannot Move that turn but may otherwise act normally. A model with this special rule gains no Cavalry Charge bonuses.</t>
   </si>
   <si>
     <t xml:space="preserve">transfix.name</t>
@@ -1231,20 +1888,55 @@
     <t xml:space="preserve">tremor.description</t>
   </si>
   <si>
-    <t xml:space="preserve">Draw an imaginary 1mm line that extends D3+3" directly away from the caster in a direction chosen by the caster. This Magical Power targets every model (friend or foe) that lies under the line. Each target immediately suffers one Strength 4 hit and is knocked Prone; if the target was a Cavalry model, they will automatically count as suffering the Knocked Flying result on the Thrown Rider Chart. If a target is Engaged in Combat, then any other model Engaged in the same Combat is also considered to be a target - make sure to Pair Off Combats before working out which models are targets. 
-Models with the Fly special rule can never be a target of this Magical Power under any circumstances.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tusk-weapons.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tusk Weapons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tusk-weapons.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">When the Mumak Tramples, it will Inflict 4 Strength 9 Impact Hits rather than 3.</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Draw an imaginary 1mm line that extends D3+3" directly away from the caster in a direction chosen by the caster. This Magical Power targets every model (friend or foe) that lies under the line. Each target immediately suffers one Strength 4 hit and is knocked Prone; if the target was a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Cavalry</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;/b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> model, they will automatically count as suffering the Knocked Flying result on the Thrown Rider Chart. If a target is Engaged in Combat, then any other model Engaged in the same Combat is also considered to be a target - make sure to Pair Off Combats before working out which models are targets. 
+Models with the &lt;rule id="fly"&gt;Fly&lt;/rule&gt; special rule can never be a target of this Magical Power under any circumstances.</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">unyielding-combat-stance.name</t>
@@ -1293,7 +1985,73 @@
     <t xml:space="preserve">wither.description</t>
   </si>
   <si>
-    <t xml:space="preserve">This Magical Power targets one enemy model in range. The target immediately reduces their Strength value by 1 for the remainder of the game. A model can be affected by this Magical Power multiple times over the course of the battle, reducing its Strength value each time. Should a model ever have its Strength reduced to 0, they are immediately slain and removed as a casualty. If this Magical Power targets a Cavalry model, the caster must choose whether the rider or the Mount is the target.</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">This Magical Power targets one enemy model in range. The target immediately reduces their Strength value by 1 for the remainder of the game. A model can be affected by this Magical Power multiple times over the course of the battle, reducing its Strength value each time. Should a model ever have its Strength reduced to 0, they are immediately slain and removed as a casualty. If this Magical Power targets a &lt;b&gt;Cavalry</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;/b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> model, the caster must choose whether the rider or the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Mount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;/b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> is the target.</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">woodland-creature.name</t>
@@ -1305,7 +2063,7 @@
     <t xml:space="preserve">woodland-creature.description</t>
   </si>
   <si>
-    <t xml:space="preserve">A model with this special rule may Move through woods and forests that are classed as Difficult Terrain as if they are Open Ground. If a Cavalry model has this special rule, but their Mount does not, then this rule does not apply to the Mount. If a Mount has this special rule, then they will still gain their Cavalry Charge bonuses when they Charge, even if the rider does not have this special rule.</t>
+    <t xml:space="preserve">A model with this special rule may Move through woods and forests that are classed as Difficult Terrain as if they are Open Ground. If a &lt;b&gt;Cavalry&lt;/b&gt; model has this special rule, but their &lt;b&gt;Mount&lt;/b&gt; does not, then this rule does not apply to the &lt;b&gt;Mount&lt;/b&gt;. If a &lt;b&gt;Mount&lt;/b&gt; has this special rule, then they will still gain their Cavalry Charge bonuses when they Charge, even if the rider does not have this special rule. &lt;u&gt;This special rule may be used by models that are not yet on the battlefield.&lt;/u&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">wrath-of-bruinen.name</t>
@@ -1317,7 +2075,54 @@
     <t xml:space="preserve">wrath-of-bruinen.description</t>
   </si>
   <si>
-    <t xml:space="preserve">This Magical Power targets all enemy models within range, even if they are not in Line of Sight of the caster. All target models immediately suffer one Strength 2 hit and are knocked Prone. Cavalry models are automatically treated as suffering a Knocked Flying result on the Thrown Rider Chart. If a target is within a water feature, they will suffer one Strength 8 hit instead of one Strength 2 hit.</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">This Magical Power targets all enemy models within range, even if they are not in Line of Sight of the caster. All target models immediately suffer one Strength 2 hit and are knocked Prone. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Cavalry</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;/b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> models are automatically treated as suffering a Knocked Flying result on the Thrown Rider Chart. If a target is within a water feature, they will suffer one Strength 8 hit instead of one Strength 2 hit.</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">writhing-vines.name</t>
@@ -1365,11 +2170,58 @@
     <t xml:space="preserve">barge.description</t>
   </si>
   <si>
-    <t xml:space="preserve">When a &lt;b&gt;Monster&lt;/b&gt; wishes to use this Brutal Power Attack, enemymodelsdo not Back Away as normal. Instead, all enemy models involved in the Combat, plus any enemy models that were Supporting, must Back Away3" rather than 1". The order and direction that these models Back Away is chosen by the &lt;b&gt;Monster&lt;/b&gt; model’s controlling player. Models may still Make Way for losing models (which will be decided by the &lt;b&gt;Monster&lt;/b&gt; model’s controlling player) and, if they do, must Make Way 3" rather than the usual 1", in a direction chosen by the &lt;b&gt;Monster&lt;/b&gt; model’s controlling player.
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">When a &lt;b&gt;Monster&lt;/b&gt; wishes to use this Brutal Power Attack, enemy models do not Back Away as normal. Instead, all enemy models involved in the Combat, plus any enemy models that were Supporting, must Back Away 3" rather than 1". The order and direction that these models Back Away is chosen by the &lt;b&gt;Monster&lt;/b&gt; model’s controlling player. Models may still Make Way for losing models (which will be decided by the &lt;b&gt;Monster&lt;/b&gt; model’s controlling player) and, if they do, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;u&gt;may&lt;/u&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Make Way 3" rather than the usual 1", in a direction chosen by the &lt;b&gt;Monster&lt;/b&gt; model’s controlling player. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;u&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">When a model Makes Way in this manner, it will only do so the minimum amount it needs to in order to allow the model Backing Away to Back Away 3"; it won’t be forced to Make Way a full 3" if only Making Way 1" would suffice to allow the Barged model to Back Away 3", for example, and won’t be automatically knocked Prone if it is able to Make Way the required amount.&lt;/u&gt;
 Any models that cannot Back Away or Make Way the full 3" are moved as far as possible and then knocked Prone. When doing this, if it is possible for a &lt;b&gt;Monster&lt;/b&gt; to choose a direction for a model to Back Away or Make Way so that it goes the full 3", then it must choose that direction–it can’t force a model to Back Away or Make Way less than 3" and be knocked Prone if there was a way for it to Back Away the full 3".
 Once a &lt;b&gt;Monster&lt;/b&gt; model has used a Barge, the Combat immediately ends and no further Strikes or Brutal Power Attacks can be made.
 Once all models have Backed Away, the &lt;b&gt;Monster&lt;/b&gt; that made the Barge can then Move D3+3" in any direction, following all the usual rules for Moving a model. It can even Charge again if it wishes, in which case it will fight again that Fight Phase in the ordinary way – i.e., in an order chosen by the player with Priority.
 A &lt;b&gt;Monster&lt;/b&gt; cannot Barge in the same turn in which it participates in a Heroic Combat.</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">hurl.name</t>
@@ -1387,7 +2239,7 @@
 &lt;li&gt; The &lt;b&gt;Monster&lt;/b&gt; rolls a D3 and adds the difference in Strength between the &lt;b&gt;Monster&lt;/b&gt; and the nominated model – this is the Hurl Distance.&lt;/li&gt;
 &lt;li&gt;The &lt;b&gt;Monster&lt;/b&gt; must then take an Intelligence Test (if the &lt;b&gt;Monster&lt;/b&gt; is also a &lt;b&gt;Mount&lt;/b&gt;, it may use the Intelligence of its rider if it is better).&lt;/li&gt;
 &lt;li&gt;If the test is passed, the &lt;b&gt;Monster&lt;/b&gt; chooses an enemy model it can draw Line of Sight to, and within the Hurl Distance from itself, to Hurl the nominated model at – this is the target. A model can only be chosen as the target of a Hurl once per turn. If the test was failed, the opposing player may choose one of their models in Line of Sight of the &lt;b&gt;Monster&lt;/b&gt;, and within the Hurl Distance, to be the target instead.&lt;/li&gt;
-&lt;li&gt;The Hurled model suffers two Strength 6 hits (if it is a &lt;b&gt;Cavalry&lt;/b&gt; model then both rider and &lt;b&gt;Mount&lt;/b&gt; will suffer these hits), and if it was a &lt;b&gt;Cavalry&lt;/b&gt; model then it is also Knocked Flying. If it is slain, skip the next step and move straight to step 6.&lt;/li&gt;
+&lt;li&gt;The Hurled model suffers two Strength 6 hits (if it is a &lt;b&gt;Cavalry&lt;/b&gt; model then both rider and &lt;b&gt;Mount&lt;/b&gt; will suffer these hits), and if it was a Cavalry model then it is also Knocked Flying &lt;u&gt;unless either the rider and/or &lt;b&gt;Mount&lt;/b&gt; have a Strength of 6 or higher&lt;/u&gt;. If it is slain, skip the next step and move straight to step 6.&lt;/li&gt;
 &lt;li&gt;If it survives, place it in base contact with the target model as close to the &lt;b&gt;Monster&lt;/b&gt; as possible. If this is not possible, place the model in base contact with the target as close to the position it should have been in as possible. If there is nowhere to place the model in base contact with the target, move other models the minimum distance to make this possible. The Hurled model is then knocked Prone.&lt;/li&gt;
 &lt;li&gt;The target model is then knocked Prone, if it has a Strength of 5 or less, and will suffer one Strength 6 hit (if it is a &lt;b&gt;Cavalry&lt;/b&gt; model then both rider and &lt;b&gt;Mount&lt;/b&gt; will suffer these hits). If it is a &lt;b&gt;Cavalry&lt;/b&gt; model then it is also Knocked Flying.&lt;/li&gt;
 &lt;li&gt;If there are no enemy models eligible to be the target, then the &lt;b&gt;Monster&lt;/b&gt; may choose a point on the battlefield it can draw Line of Sight within the Hurl Distance instead. Place the Hurled model on the chosen point; it is then knocked Prone and suffers two Strength 6 hits.&lt;/li&gt;
@@ -1450,31 +2302,13 @@
     <t xml:space="preserve">Spear</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">spear</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.description</t>
-    </r>
+    <t xml:space="preserve">spear.description</t>
   </si>
   <si>
     <t xml:space="preserve">An &lt;b&gt;Infantry&lt;/b&gt; model armed with a spear may assist a friendly model during a Combat, so long as their ally has the same base size or smaller – this is called Supporting.
 If a spear-armed model is not Engaged in Combat, then it can Support a friendly model in base contact. When they do, they contribute a single dice to the Duel Roll of the Combat the model they are Supportingispartof. This dice uses the Supporting model’s own Fight Value, and if they win they will make a single Strike using their own Strength. In a Multiple Combat, a Supporting model doesn’t have to Strike the same model as the model it is Supporting.
 Models that are Supporting do not count as being involved in the Combat they are Supporting. As a result, they cannot be targeted by Strikes, will not be knocked Prone by a Charging &lt;b&gt;Cavalry&lt;/b&gt; model, cannot benefit from a Heroic Combat, and never count as being part of the Combat for the purpose of special rules or determining how many models are taking part on each side.
-A spear-armed model can only Support a single Combat during each Fight Phase. A spear-armed model cannot Support a Combat after already being Engaged in Combat. The only exception to this is that a spear-armed model that is involved in a successful Heroic Combat, and therefore gets to Move, may Move to Support a Combat, provided it hasn’t Supported an other Combat that Fight Phase.
+&lt;u&gt;A model can only gain Support from one spear-armed model at a time. Additionally&lt;/u&gt;, spear-armed model can only Support a single Combat during each Fight Phase. A spear-armed model cannot Support a Combat after already being Engaged in Combat. The only exception to this is that a spear-armed model that is involved in a successful Heroic Combat, and therefore gets to Move, may Move to Support a Combat, provided it hasn’t Supported an other Combat that Fight Phase.
 A model with a spear can use it as a hand weapon when they are Engaged in Combat. A model can’t Support if it is Prone, rendered unable to Activate or has made a Shooting Attack during the same turn.
 A Hero that is Supporting may use Might Points to improve a Duel Roll or To Wound Rolls as normal. However, a Hero that has declared a Heroic Action in the Fight Phase cannot Support during that Fight Phase.</t>
   </si>
@@ -1485,25 +2319,7 @@
     <t xml:space="preserve">Pike</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">pike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.description</t>
-    </r>
+    <t xml:space="preserve">pike.description</t>
   </si>
   <si>
     <t xml:space="preserve">Pikes function in much the same way as spears, and allow models to Support in exactly the same way as those armed with a spear (see &lt;rule id="spear"&gt;spear&lt;/rule&gt;).
@@ -1519,25 +2335,7 @@
     <t xml:space="preserve">Lance</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">lance</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.description</t>
-    </r>
+    <t xml:space="preserve">lance.description</t>
   </si>
   <si>
     <t xml:space="preserve">A &lt;b&gt;Cavalry&lt;/b&gt; model using a lance applies a +1 modifier on any To Wound Rolls when making Strikes in a Combat in which it Charged. This modifier is not applied if the &lt;b&gt;Cavalry&lt;/b&gt; model Charges whilst within Difficult Terrain.
@@ -1550,25 +2348,7 @@
     <t xml:space="preserve">War spear</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">war-spear</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.description</t>
-    </r>
+    <t xml:space="preserve">war-spear.description</t>
   </si>
   <si>
     <t xml:space="preserve">A war spear follows the rules for a spear when wielded by an &lt;b&gt;Infantry&lt;/b&gt; model, and follows the rules for a lance when wielded by a &lt;b&gt;Cavalry&lt;/b&gt; model. The only exception is that a Cavalry model doesn’t have to discard the war spear when they Dismount or lose their &lt;b&gt;Mount&lt;/b&gt;.</t>
@@ -1580,25 +2360,7 @@
     <t xml:space="preserve">Whip</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">whip</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.description</t>
-    </r>
+    <t xml:space="preserve">whip.description</t>
   </si>
   <si>
     <t xml:space="preserve">A whip counts as a throwing weapon with a Strengthof 1 and a range of 2". It can also be used as a handweapon in a Combat.</t>
@@ -1610,25 +2372,7 @@
     <t xml:space="preserve">Elven weapon</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">elven-weapon</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.description</t>
-    </r>
+    <t xml:space="preserve">elven-weapon.description</t>
   </si>
   <si>
     <t xml:space="preserve">Some weapons will be described as an Elven weapon; for example, a model may have an Elven hand weapon or an Elven two-handed weapon.
@@ -1643,25 +2387,7 @@
     <t xml:space="preserve">Master-forged</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">master-forged</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.description</t>
-    </r>
+    <t xml:space="preserve">master-forged.description</t>
   </si>
   <si>
     <t xml:space="preserve">Some weapons may be classed as Master-forged. A model using a Master-forged weapon doesn't suffer the -1 penalty to the Duel Roll for using it as a &lt;rule id="two-handed-weapon"&gt;two-handed weapon&lt;/rule&gt;.</t>
@@ -1673,25 +2399,7 @@
     <t xml:space="preserve">Staff of Power</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">staff-of-power</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.description</t>
-    </r>
+    <t xml:space="preserve">staff-of-power.description</t>
   </si>
   <si>
     <t xml:space="preserve">A Staff of Power is a &lt;rule id="hand-and-a-half-weapon"&gt;hand-and-a-half weapon&lt;/rule&gt;. Additionally, the wielder of a Staff of Power gains a free Will Point at the start of each turn. If this free Will Point is not spent by the end of the turn, it is lost.</t>
@@ -1703,25 +2411,7 @@
     <t xml:space="preserve">Bow</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">bow</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.description</t>
-    </r>
+    <t xml:space="preserve">bow.description</t>
   </si>
   <si>
     <t xml:space="preserve">The term bow covers a wide range of Missile Weapons, including bows, longbows, Elf bows, Dwarf bows, and so on – essentially any Missile Weapon with ‘bow’ in its name (with the exception of a &lt;rule id="crossbow"&gt;crossbow&lt;/rule&gt;). All bows function the same; a model can make a Shooting Attack with a bow during the Shoot Phase provided it has not Moved over half its Move Value during the preceding Move Phase.
@@ -1734,25 +2424,7 @@
     <t xml:space="preserve">Throwing weapon</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">throwing-weapon</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.description</t>
-    </r>
+    <t xml:space="preserve">throwing-weapon.description</t>
   </si>
   <si>
     <t xml:space="preserve">A model with a throwing weapon can make a Shooting Attack with it in the Shoot Phase, even if it Moved its full Move Value in the preceding Move Phase.
@@ -1768,25 +2440,7 @@
     <t xml:space="preserve">Crossbow</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">crossbow</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.description</t>
-    </r>
+    <t xml:space="preserve">crossbow.description</t>
   </si>
   <si>
     <t xml:space="preserve">A model with a crossbow cannot make a Shooting Attack with it in the same turn in which it Moved.</t>
@@ -1798,25 +2452,7 @@
     <t xml:space="preserve">Blowpipe</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">blowpipe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.description</t>
-    </r>
+    <t xml:space="preserve">blowpipe.description</t>
   </si>
   <si>
     <t xml:space="preserve">A model with a blowpipe can make a Shooting Attack with it in the Shoot Phase provided it has not Moved over half its Move Value during the preceding Move Phase. Additionally, a blowpipe benefits from the Poisoned Attacks special rule.
@@ -1829,25 +2465,7 @@
     <t xml:space="preserve">Sling</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">sling</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.description</t>
-    </r>
+    <t xml:space="preserve">sling.description</t>
   </si>
   <si>
     <t xml:space="preserve">A model with a sling can make two Shooting Attacks with it in the Shoot Phase, providing they did not Move at all during the preceding Move Phase. If the model Moved up to half their Move Value in the preceding Move Phase, they may make a single Shooting Attack. If they Moved over half their Move Value in the preceding Move Phase, they may not make a Shooting Attack in the Shoot Phase.</t>
@@ -1859,25 +2477,7 @@
     <t xml:space="preserve">Banner</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">banner</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.description</t>
-    </r>
+    <t xml:space="preserve">banner.description</t>
   </si>
   <si>
     <t xml:space="preserve">A banner has a 3" area of effect that extends out from the model carrying the banner (although some special banners may have a larger range). If a friendly model is within the range of one or more friendly banners, can draw Line of Sight to that banner, and is either Engaged in Combat or Supporting a friendly model, then that Combat is affected by the banner. If a Combat is affected by a banner then a single friendly model in that Combat (including a Supporting model) can re-roll a single dice in the Duel Roll. If a Combat is affected by multiple friendly banners, then this will still only allow a single dice to be re-rolled as part of the Duel Roll, not one for each banner. A model cannot use a banner to re-roll a dice in a Duel Roll that the model is currently winning, in order to try to lose the Combat.
@@ -1895,25 +2495,7 @@
     <t xml:space="preserve">Elven cloak</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">elven-cloak</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.description</t>
-    </r>
+    <t xml:space="preserve">elven-cloak.description</t>
   </si>
   <si>
     <t xml:space="preserve">A model wearing an Elven cloak has the Stalk Unseen special rule. Additionally, models targeting an &lt;b&gt;Infantry&lt;/b&gt; model wearing an Elven cloak with a Shooting Attack suffer a -1 penalty when rolling To Hit.</t>
@@ -1925,25 +2507,7 @@
     <t xml:space="preserve">War drum</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">war-drum</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.description</t>
-    </r>
+    <t xml:space="preserve">war-drum.description</t>
   </si>
   <si>
     <t xml:space="preserve">A model with a war drum may use it during the Declare Heroic Actions step of each Move Phase to declare a &lt;rule id="heroic-march"&gt;Heroic March&lt;/rule&gt; for free, without spending a Might Point, even if they are not a &lt;b&gt;Hero&lt;/b&gt;. This free Heroic March has the following exceptions:
@@ -1962,25 +2526,7 @@
     <t xml:space="preserve">War horn</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">war-horn</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.description</t>
-    </r>
+    <t xml:space="preserve">war-horn.description</t>
   </si>
   <si>
     <t xml:space="preserve">Models within 24" of a friendly model with a war horn gain a bonus of +1 to any Courage Tests they take. Additionally, a model with a war horn gains the &lt;rule id="dominant"&gt;Dominant (2)&lt;/rule&gt; special rule and can use it once per game to increase the range of a friendly &lt;b&gt;Hero&lt;/b&gt; model’s Stand Fast by 3", so long as the model with the war horn is in range of the &lt;b&gt;Hero&lt;/b&gt; model’s Stand Fast before this increase. If a &lt;b&gt;Hero&lt;/b&gt; model has a war horn themselves, they may use it to increase the range of their own Stand Fast by 3" instead. A war horn is treated as an Active ability (see page 123).</t>
@@ -1992,25 +2538,7 @@
     <t xml:space="preserve">Armour</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">armour</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.description</t>
-    </r>
+    <t xml:space="preserve">armour.description</t>
   </si>
   <si>
     <t xml:space="preserve">A model wearing armour will add 1 to their Defence characteristic</t>
@@ -2022,25 +2550,7 @@
     <t xml:space="preserve">Light armour</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">light-armour</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.description</t>
-    </r>
+    <t xml:space="preserve">light-armour.description</t>
   </si>
   <si>
     <t xml:space="preserve">A model wearing light armour will add 1 to their Defence characteristic against Shooting Attacks. If a model is wearing light armour then the Defence improvement will not have been added onto their profile.</t>
@@ -2052,25 +2562,7 @@
     <t xml:space="preserve">Heavy armour</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">heavy-armour</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.description</t>
-    </r>
+    <t xml:space="preserve">heavy-armour.description</t>
   </si>
   <si>
     <t xml:space="preserve">A model wearing heavy armour will add 2 to their Defence characteristic.</t>
@@ -2082,25 +2574,7 @@
     <t xml:space="preserve">Heavy Dwarf armour</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">heavy-dwarf-armour</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.description</t>
-    </r>
+    <t xml:space="preserve">heavy-dwarf-armour.description</t>
   </si>
   <si>
     <t xml:space="preserve">A model wearing heavy Dwarf armour will add 3 to their Defence characteristic.</t>
@@ -2112,25 +2586,7 @@
     <t xml:space="preserve">Mithril armour</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">mithril-armour</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.description</t>
-    </r>
+    <t xml:space="preserve">mithril-armour.description</t>
   </si>
   <si>
     <t xml:space="preserve">A model wearing Mithril armour will add 3 to their Defence characteristic. Additionally, &lt;b&gt;Monster&lt;/b&gt; models cannot use the &lt;rule id="rend"&gt;Rend&lt;/rule&gt; Brutal Power Attack against a model wearing Mithril armour.</t>
@@ -2142,32 +2598,14 @@
     <t xml:space="preserve">Shield</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">shield</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.description</t>
-    </r>
+    <t xml:space="preserve">shield.description</t>
   </si>
   <si>
     <t xml:space="preserve">A model carrying a shield adds 1 to their Defence characteristic. Where a model is listed as carrying a shield in its profile, then the improvement in its Defence characteristic will already have been included in their profile.
 A shield is cumbersome, and so a model carrying a shield that wishes to use their &lt;rule id="hand-and-a-half-weapon"&gt;hand-and-a-half weapon&lt;/rule&gt; as a &lt;rule id="two-handed-weapon"&gt;two-handed weapon&lt;/rule&gt; during a Combat cannot gain the Defence bonus for carrying a shield during that Combat. Additionally, a model carrying a shield does not gain the Defence bonus if it also carries a type of bow, crossbow, two-handed weapon or &lt;rule id="pike"&gt;pike&lt;/rule&gt;.
 A model with a shield can also use the Shielding special rule:
 &lt;h3&gt;Shielding&lt;/h3&gt;
-A model carrying a shield may declare they are Shielding at the start of a Combat they are involved in, before the Duel Roll is made. If they do, the Shielding model will double their Attacks characteristic for the duration of the Combat; however, if they win the Duel Roll they cannot make Strikes having put their effort into surviving. They also don’t gain any advantages of the special rules of their weapons (such as if they have an Elven weapon) as they are not using them in the Combat and are using their shield instead.
+A model carrying a shield may declare they are Shielding at the start of a Combat they are involved in, before the Duel Roll is made. If they do, the Shielding model will double their Attacks characteristic for the duration of the Combat; however, if they win the Duel Roll they cannot make Strikes having put their effort into surviving. &lt;u&gt;They also don’t gain any advantages of the special rules of their weapons (such as if they have an Elven weapon) as they are not using them in the Combat and are using their shield instead.&lt;/u&gt;
 In a Multiple Combat, if one model wishes to declare they are Shielding, then all friendly models must do so. If some of them cannot, then no models may declare they are Shielding. Models that are Shielding cannot be Supported.
 &lt;b&gt;Cavalry&lt;/b&gt; models cannot declare they are Shielding. Additionally, Shielding is treated as an Active ability (see page 123).
 A Prone model can declare they are Shielding – infact, it is a sensible way of trying to get them to stand backup as a Prone model can’t make Strikes anyway!</t>
@@ -2179,25 +2617,7 @@
     <t xml:space="preserve">Light shield</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">light-shield</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.description</t>
-    </r>
+    <t xml:space="preserve">light-shield.description</t>
   </si>
   <si>
     <t xml:space="preserve">A model with a light shield does not gain a bonus to its Defence. However, it may use the Shielding special rule as described on the &lt;rule id="shield"&gt;Shield&lt;/rule&gt; equipment.</t>
@@ -2282,7 +2702,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2293,22 +2713,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -2332,7 +2736,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B267"/>
+  <dimension ref="A1:B1048576"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="48.83"/>
@@ -2340,7 +2744,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="3" style="1" width="8.5"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2348,7 +2752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -2356,7 +2760,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -2364,7 +2768,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -2372,7 +2776,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="114.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -2380,7 +2784,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -2388,7 +2792,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -2396,7 +2800,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -2404,7 +2808,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
@@ -2412,7 +2816,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
@@ -2420,7 +2824,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
@@ -2428,7 +2832,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
@@ -2436,7 +2840,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
@@ -2444,7 +2848,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
         <v>26</v>
       </c>
@@ -2452,7 +2856,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
         <v>28</v>
       </c>
@@ -2460,7 +2864,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
         <v>30</v>
       </c>
@@ -2468,7 +2872,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
         <v>32</v>
       </c>
@@ -2476,7 +2880,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
         <v>34</v>
       </c>
@@ -2484,7 +2888,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
         <v>36</v>
       </c>
@@ -2492,7 +2896,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
         <v>38</v>
       </c>
@@ -2500,7 +2904,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
         <v>40</v>
       </c>
@@ -2508,7 +2912,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
         <v>42</v>
       </c>
@@ -2516,7 +2920,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
         <v>44</v>
       </c>
@@ -2524,7 +2928,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
         <v>46</v>
       </c>
@@ -2532,7 +2936,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
         <v>48</v>
       </c>
@@ -2540,7 +2944,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
         <v>50</v>
       </c>
@@ -2548,7 +2952,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="100.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
         <v>52</v>
       </c>
@@ -2556,7 +2960,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
         <v>54</v>
       </c>
@@ -2564,7 +2968,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="72.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
         <v>56</v>
       </c>
@@ -2572,7 +2976,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
         <v>58</v>
       </c>
@@ -2580,7 +2984,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
         <v>60</v>
       </c>
@@ -2588,7 +2992,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
         <v>62</v>
       </c>
@@ -2596,7 +3000,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
         <v>64</v>
       </c>
@@ -2604,7 +3008,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
         <v>66</v>
       </c>
@@ -2612,7 +3016,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
         <v>68</v>
       </c>
@@ -2620,7 +3024,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
         <v>70</v>
       </c>
@@ -2628,7 +3032,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
         <v>72</v>
       </c>
@@ -2636,7 +3040,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
         <v>74</v>
       </c>
@@ -2644,7 +3048,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="100.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
         <v>76</v>
       </c>
@@ -2652,7 +3056,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
         <v>78</v>
       </c>
@@ -2660,7 +3064,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="100.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
         <v>80</v>
       </c>
@@ -2668,7 +3072,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
         <v>82</v>
       </c>
@@ -2676,7 +3080,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="86.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
         <v>84</v>
       </c>
@@ -2684,7 +3088,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
         <v>86</v>
       </c>
@@ -2692,7 +3096,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="72.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
         <v>88</v>
       </c>
@@ -2700,7 +3104,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
         <v>90</v>
       </c>
@@ -2708,7 +3112,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="72.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
         <v>92</v>
       </c>
@@ -2716,7 +3120,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
         <v>94</v>
       </c>
@@ -2724,7 +3128,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
         <v>96</v>
       </c>
@@ -2732,7 +3136,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
         <v>98</v>
       </c>
@@ -2740,7 +3144,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
         <v>100</v>
       </c>
@@ -2748,7 +3152,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
         <v>102</v>
       </c>
@@ -2756,7 +3160,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
         <v>104</v>
       </c>
@@ -2764,7 +3168,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
         <v>106</v>
       </c>
@@ -2772,7 +3176,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
         <v>108</v>
       </c>
@@ -2780,7 +3184,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
         <v>110</v>
       </c>
@@ -2788,7 +3192,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
         <v>112</v>
       </c>
@@ -2796,7 +3200,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
         <v>114</v>
       </c>
@@ -2804,7 +3208,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
         <v>116</v>
       </c>
@@ -2812,7 +3216,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
         <v>118</v>
       </c>
@@ -2820,7 +3224,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
         <v>120</v>
       </c>
@@ -2828,7 +3232,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
         <v>122</v>
       </c>
@@ -2836,7 +3240,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="256.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
         <v>124</v>
       </c>
@@ -2844,7 +3248,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
         <v>126</v>
       </c>
@@ -2852,7 +3256,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
         <v>128</v>
       </c>
@@ -2860,7 +3264,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
         <v>130</v>
       </c>
@@ -2868,7 +3272,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
         <v>132</v>
       </c>
@@ -2876,7 +3280,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
         <v>134</v>
       </c>
@@ -2884,7 +3288,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="270.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
         <v>136</v>
       </c>
@@ -2892,7 +3296,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
         <v>138</v>
       </c>
@@ -2900,7 +3304,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
         <v>140</v>
       </c>
@@ -2908,7 +3312,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
         <v>142</v>
       </c>
@@ -2916,7 +3320,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
         <v>144</v>
       </c>
@@ -2924,7 +3328,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
         <v>146</v>
       </c>
@@ -2932,7 +3336,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
         <v>148</v>
       </c>
@@ -2940,7 +3344,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
         <v>150</v>
       </c>
@@ -2948,7 +3352,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
         <v>152</v>
       </c>
@@ -2956,7 +3360,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
         <v>154</v>
       </c>
@@ -2964,7 +3368,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="199.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
         <v>156</v>
       </c>
@@ -2972,7 +3376,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
         <v>158</v>
       </c>
@@ -2980,7 +3384,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="270.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
         <v>160</v>
       </c>
@@ -2988,7 +3392,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
         <v>162</v>
       </c>
@@ -2996,7 +3400,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2" t="s">
         <v>164</v>
       </c>
@@ -3004,7 +3408,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
         <v>166</v>
       </c>
@@ -3012,7 +3416,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="213.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
         <v>168</v>
       </c>
@@ -3020,7 +3424,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
         <v>170</v>
       </c>
@@ -3028,7 +3432,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
         <v>172</v>
       </c>
@@ -3036,7 +3440,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
         <v>174</v>
       </c>
@@ -3044,7 +3448,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="384.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="s">
         <v>176</v>
       </c>
@@ -3052,7 +3456,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
         <v>178</v>
       </c>
@@ -3060,7 +3464,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="270.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="497.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
         <v>180</v>
       </c>
@@ -3068,7 +3472,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
         <v>182</v>
       </c>
@@ -3076,7 +3480,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="128.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
         <v>184</v>
       </c>
@@ -3084,7 +3488,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
         <v>186</v>
       </c>
@@ -3092,7 +3496,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="214.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="157.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
         <v>188</v>
       </c>
@@ -3100,7 +3504,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
         <v>190</v>
       </c>
@@ -3108,7 +3512,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
         <v>192</v>
       </c>
@@ -3116,7 +3520,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
         <v>194</v>
       </c>
@@ -3124,7 +3528,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="384.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
         <v>196</v>
       </c>
@@ -3132,7 +3536,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
         <v>198</v>
       </c>
@@ -3140,7 +3544,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="497.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
         <v>200</v>
       </c>
@@ -3148,7 +3552,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
         <v>202</v>
       </c>
@@ -3156,7 +3560,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="129.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
         <v>204</v>
       </c>
@@ -3164,7 +3568,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
         <v>206</v>
       </c>
@@ -3172,7 +3576,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="157.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="270.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
         <v>208</v>
       </c>
@@ -3180,7 +3584,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
         <v>210</v>
       </c>
@@ -3188,7 +3592,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
         <v>212</v>
       </c>
@@ -3196,7 +3600,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
         <v>214</v>
       </c>
@@ -3204,7 +3608,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
         <v>216</v>
       </c>
@@ -3212,7 +3616,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="s">
         <v>218</v>
       </c>
@@ -3220,7 +3624,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2" t="s">
         <v>220</v>
       </c>
@@ -3228,7 +3632,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="2" t="s">
         <v>222</v>
       </c>
@@ -3236,7 +3640,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="s">
         <v>224</v>
       </c>
@@ -3244,7 +3648,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
         <v>226</v>
       </c>
@@ -3252,7 +3656,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="270.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="s">
         <v>228</v>
       </c>
@@ -3260,7 +3664,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="s">
         <v>230</v>
       </c>
@@ -3268,7 +3672,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
         <v>232</v>
       </c>
@@ -3276,7 +3680,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
         <v>234</v>
       </c>
@@ -3284,7 +3688,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="100.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
         <v>236</v>
       </c>
@@ -3292,7 +3696,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="s">
         <v>238</v>
       </c>
@@ -3300,7 +3704,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
         <v>240</v>
       </c>
@@ -3308,7 +3712,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
         <v>242</v>
       </c>
@@ -3316,7 +3720,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="s">
         <v>244</v>
       </c>
@@ -3324,7 +3728,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2" t="s">
         <v>246</v>
       </c>
@@ -3332,7 +3736,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="157.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
         <v>248</v>
       </c>
@@ -3340,7 +3744,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="s">
         <v>250</v>
       </c>
@@ -3348,7 +3752,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
         <v>252</v>
       </c>
@@ -3356,7 +3760,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2" t="s">
         <v>254</v>
       </c>
@@ -3364,7 +3768,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="2" t="s">
         <v>256</v>
       </c>
@@ -3372,7 +3776,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2" t="s">
         <v>258</v>
       </c>
@@ -3380,7 +3784,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2" t="s">
         <v>260</v>
       </c>
@@ -3388,7 +3792,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="2" t="s">
         <v>262</v>
       </c>
@@ -3396,7 +3800,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2" t="s">
         <v>264</v>
       </c>
@@ -3404,7 +3808,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="2" t="s">
         <v>266</v>
       </c>
@@ -3412,7 +3816,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="157.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="100.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="s">
         <v>268</v>
       </c>
@@ -3420,7 +3824,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2" t="s">
         <v>270</v>
       </c>
@@ -3428,7 +3832,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="2" t="s">
         <v>272</v>
       </c>
@@ -3436,7 +3840,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2" t="s">
         <v>274</v>
       </c>
@@ -3444,7 +3848,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="s">
         <v>276</v>
       </c>
@@ -3452,7 +3856,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
         <v>278</v>
       </c>
@@ -3460,7 +3864,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="86.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="2" t="s">
         <v>280</v>
       </c>
@@ -3468,7 +3872,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="2" t="s">
         <v>282</v>
       </c>
@@ -3476,7 +3880,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2" t="s">
         <v>284</v>
       </c>
@@ -3484,7 +3888,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2" t="s">
         <v>286</v>
       </c>
@@ -3492,7 +3896,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="2" t="s">
         <v>288</v>
       </c>
@@ -3500,7 +3904,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2" t="s">
         <v>290</v>
       </c>
@@ -3508,7 +3912,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="2" t="s">
         <v>292</v>
       </c>
@@ -3516,7 +3920,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2" t="s">
         <v>294</v>
       </c>
@@ -3524,7 +3928,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="2" t="s">
         <v>296</v>
       </c>
@@ -3532,7 +3936,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2" t="s">
         <v>298</v>
       </c>
@@ -3540,7 +3944,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="86.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="2" t="s">
         <v>300</v>
       </c>
@@ -3548,7 +3952,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="2" t="s">
         <v>302</v>
       </c>
@@ -3556,7 +3960,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="2" t="s">
         <v>304</v>
       </c>
@@ -3564,7 +3968,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="2" t="s">
         <v>306</v>
       </c>
@@ -3572,7 +3976,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="2" t="s">
         <v>308</v>
       </c>
@@ -3580,7 +3984,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2" t="s">
         <v>310</v>
       </c>
@@ -3588,7 +3992,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="171.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2" t="s">
         <v>312</v>
       </c>
@@ -3596,7 +4000,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2" t="s">
         <v>314</v>
       </c>
@@ -3604,7 +4008,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="72.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="2" t="s">
         <v>316</v>
       </c>
@@ -3612,7 +4016,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="2" t="s">
         <v>318</v>
       </c>
@@ -3620,7 +4024,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2" t="s">
         <v>320</v>
       </c>
@@ -3628,7 +4032,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="2" t="s">
         <v>322</v>
       </c>
@@ -3636,7 +4040,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="2" t="s">
         <v>324</v>
       </c>
@@ -3644,7 +4048,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="2" t="s">
         <v>326</v>
       </c>
@@ -3652,7 +4056,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="100.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="2" t="s">
         <v>328</v>
       </c>
@@ -3660,7 +4064,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="2" t="s">
         <v>330</v>
       </c>
@@ -3668,7 +4072,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="2" t="s">
         <v>332</v>
       </c>
@@ -3676,7 +4080,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="2" t="s">
         <v>334</v>
       </c>
@@ -3684,7 +4088,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="2" t="s">
         <v>336</v>
       </c>
@@ -3692,7 +4096,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="2" t="s">
         <v>338</v>
       </c>
@@ -3700,7 +4104,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="114.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="2" t="s">
         <v>340</v>
       </c>
@@ -3708,7 +4112,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="2" t="s">
         <v>342</v>
       </c>
@@ -3716,7 +4120,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="2" t="s">
         <v>344</v>
       </c>
@@ -3724,7 +4128,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="2" t="s">
         <v>346</v>
       </c>
@@ -3732,7 +4136,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="2" t="s">
         <v>348</v>
       </c>
@@ -3740,7 +4144,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="2" t="s">
         <v>350</v>
       </c>
@@ -3748,7 +4152,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="157.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="2" t="s">
         <v>352</v>
       </c>
@@ -3756,7 +4160,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="2" t="s">
         <v>354</v>
       </c>
@@ -3764,7 +4168,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="2" t="s">
         <v>356</v>
       </c>
@@ -3772,7 +4176,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="2" t="s">
         <v>358</v>
       </c>
@@ -3780,7 +4184,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="2" t="s">
         <v>360</v>
       </c>
@@ -3788,55 +4192,55 @@
         <v>361</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="2" t="s">
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B182" s="2" t="s">
+      <c r="B182" s="1" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="2" t="s">
+    <row r="183" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B183" s="2" t="s">
+      <c r="B183" s="1" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="2" t="s">
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B184" s="2" t="s">
+      <c r="B184" s="1" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="100.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="2" t="s">
+    <row r="185" customFormat="false" ht="270.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B185" s="2" t="s">
+      <c r="B185" s="1" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="2" t="s">
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B186" s="2" t="s">
+      <c r="B186" s="1" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="2" t="s">
+    <row r="187" customFormat="false" ht="369.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="1" t="s">
         <v>372</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="2" t="s">
         <v>374</v>
       </c>
@@ -3844,136 +4248,136 @@
         <v>375</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="B189" s="2" t="s">
+      <c r="B189" s="1" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="B190" s="2" t="s">
+      <c r="B190" s="1" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="114.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="B191" s="2" t="s">
+      <c r="B191" s="1" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="B192" s="2" t="s">
+      <c r="B192" s="1" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="114.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="B193" s="2" t="s">
+      <c r="B193" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="B194" s="2" t="s">
+      <c r="B194" s="1" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="B195" s="2" t="s">
+      <c r="B195" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="B196" s="2" t="s">
+      <c r="B196" s="1" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="313.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B197" s="2" t="s">
+      <c r="B197" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="B198" s="2" t="s">
+      <c r="B198" s="1" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="199.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B199" s="2" t="s">
+      <c r="B199" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B200" s="2" t="s">
+      <c r="B200" s="1" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B201" s="2" t="s">
+      <c r="B201" s="1" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B202" s="2" t="s">
+      <c r="B202" s="1" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B203" s="2" t="s">
+      <c r="B203" s="1" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="1" t="s">
+      <c r="A204" s="2" t="s">
         <v>406</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="1" t="s">
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="2" t="s">
         <v>408</v>
       </c>
       <c r="B205" s="1" t="s">
@@ -3981,15 +4385,15 @@
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="1" t="s">
+      <c r="A206" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B206" s="1" t="s">
+      <c r="B206" s="2" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="242.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="1" t="s">
+    <row r="207" customFormat="false" ht="142.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="2" t="s">
         <v>412</v>
       </c>
       <c r="B207" s="1" t="s">
@@ -3997,31 +4401,31 @@
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="1" t="s">
+      <c r="A208" s="2" t="s">
         <v>414</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="355.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="1" t="s">
+    <row r="209" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B209" s="3" t="s">
+      <c r="B209" s="1" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="4" t="s">
+      <c r="A210" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="B210" s="0" t="s">
+      <c r="B210" s="1" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="211" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="4" t="s">
+    <row r="211" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="2" t="s">
         <v>420</v>
       </c>
       <c r="B211" s="1" t="s">
@@ -4029,15 +4433,15 @@
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="4" t="s">
+      <c r="A212" s="2" t="s">
         <v>422</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="114.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="5" t="s">
+    <row r="213" customFormat="false" ht="86.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="2" t="s">
         <v>424</v>
       </c>
       <c r="B213" s="1" t="s">
@@ -4045,15 +4449,15 @@
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="4" t="s">
+      <c r="A214" s="2" t="s">
         <v>426</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="215" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="4" t="s">
+    <row r="215" customFormat="false" ht="228.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="2" t="s">
         <v>428</v>
       </c>
       <c r="B215" s="1" t="s">
@@ -4061,31 +4465,31 @@
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="4" t="s">
+      <c r="A216" s="2" t="s">
         <v>430</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="4" t="s">
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="B217" s="1" t="s">
+      <c r="B217" s="2" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="4" t="s">
+      <c r="A218" s="2" t="s">
         <v>434</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="219" customFormat="false" ht="299.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="4" t="s">
+    <row r="219" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="2" t="s">
         <v>436</v>
       </c>
       <c r="B219" s="1" t="s">
@@ -4093,15 +4497,15 @@
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="4" t="s">
+      <c r="A220" s="2" t="s">
         <v>438</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="4" t="s">
+    <row r="221" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="2" t="s">
         <v>440</v>
       </c>
       <c r="B221" s="1" t="s">
@@ -4109,15 +4513,15 @@
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="4" t="s">
+      <c r="A222" s="2" t="s">
         <v>442</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="4" t="s">
+    <row r="223" customFormat="false" ht="412.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="2" t="s">
         <v>444</v>
       </c>
       <c r="B223" s="1" t="s">
@@ -4125,15 +4529,15 @@
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="4" t="s">
+      <c r="A224" s="2" t="s">
         <v>446</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="225" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="4" t="s">
+    <row r="225" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="2" t="s">
         <v>448</v>
       </c>
       <c r="B225" s="1" t="s">
@@ -4141,15 +4545,15 @@
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="4" t="s">
+      <c r="A226" s="2" t="s">
         <v>450</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="4" t="s">
+    <row r="227" customFormat="false" ht="157.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A227" s="2" t="s">
         <v>452</v>
       </c>
       <c r="B227" s="1" t="s">
@@ -4157,15 +4561,15 @@
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="4" t="s">
+      <c r="A228" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="B228" s="6" t="s">
+      <c r="B228" s="1" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="229" customFormat="false" ht="143.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="4" t="s">
+    <row r="229" customFormat="false" ht="71.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="2" t="s">
         <v>456</v>
       </c>
       <c r="B229" s="1" t="s">
@@ -4173,31 +4577,31 @@
       </c>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="4" t="s">
+      <c r="A230" s="2" t="s">
         <v>458</v>
       </c>
       <c r="B230" s="1" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="231" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="4" t="s">
+    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="B231" s="1" t="s">
+      <c r="B231" s="2" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="4" t="s">
+      <c r="A232" s="2" t="s">
         <v>462</v>
       </c>
       <c r="B232" s="1" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="233" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="4" t="s">
+    <row r="233" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A233" s="2" t="s">
         <v>464</v>
       </c>
       <c r="B233" s="1" t="s">
@@ -4205,15 +4609,15 @@
       </c>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="4" t="s">
+      <c r="A234" s="2" t="s">
         <v>466</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="235" customFormat="false" ht="86.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="4" t="s">
+    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A235" s="2" t="s">
         <v>468</v>
       </c>
       <c r="B235" s="1" t="s">
@@ -4221,15 +4625,15 @@
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="4" t="s">
+      <c r="A236" s="2" t="s">
         <v>470</v>
       </c>
       <c r="B236" s="1" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="237" customFormat="false" ht="228.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="4" t="s">
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="2" t="s">
         <v>472</v>
       </c>
       <c r="B237" s="1" t="s">
@@ -4237,31 +4641,31 @@
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="4" t="s">
+      <c r="A238" s="2" t="s">
         <v>474</v>
       </c>
       <c r="B238" s="1" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="4" t="s">
+    <row r="239" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A239" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="B239" s="3" t="s">
+      <c r="B239" s="1" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="4" t="s">
+      <c r="A240" s="2" t="s">
         <v>478</v>
       </c>
       <c r="B240" s="1" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="241" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="4" t="s">
+    <row r="241" customFormat="false" ht="327.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A241" s="2" t="s">
         <v>480</v>
       </c>
       <c r="B241" s="1" t="s">
@@ -4269,15 +4673,15 @@
       </c>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="4" t="s">
+      <c r="A242" s="2" t="s">
         <v>482</v>
       </c>
       <c r="B242" s="1" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="243" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="4" t="s">
+    <row r="243" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="2" t="s">
         <v>484</v>
       </c>
       <c r="B243" s="1" t="s">
@@ -4285,187 +4689,33 @@
       </c>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="B244" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="245" customFormat="false" ht="412.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="4" t="s">
-        <v>488</v>
-      </c>
-      <c r="B245" s="1" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="B246" s="1" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="247" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="B247" s="1" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="4" t="s">
-        <v>494</v>
-      </c>
-      <c r="B248" s="1" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="249" customFormat="false" ht="157.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="4" t="s">
-        <v>496</v>
-      </c>
-      <c r="B249" s="1" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="4" t="s">
-        <v>498</v>
-      </c>
-      <c r="B250" s="1" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="251" customFormat="false" ht="72.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="4" t="s">
-        <v>500</v>
-      </c>
-      <c r="B251" s="1" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B252" s="1" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="4" t="s">
-        <v>504</v>
-      </c>
-      <c r="B253" s="6" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="4" t="s">
-        <v>506</v>
-      </c>
-      <c r="B254" s="1" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="255" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="4" t="s">
-        <v>508</v>
-      </c>
-      <c r="B255" s="1" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="B256" s="1" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="4" t="s">
-        <v>512</v>
-      </c>
-      <c r="B257" s="1" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="4" t="s">
-        <v>514</v>
-      </c>
-      <c r="B258" s="1" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="4" t="s">
-        <v>516</v>
-      </c>
-      <c r="B259" s="1" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="4" t="s">
-        <v>518</v>
-      </c>
-      <c r="B260" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="261" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="4" t="s">
-        <v>520</v>
-      </c>
-      <c r="B261" s="1" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A262" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="B262" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="263" customFormat="false" ht="327.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="4" t="s">
-        <v>524</v>
-      </c>
-      <c r="B263" s="1" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A264" s="4" t="s">
-        <v>526</v>
-      </c>
-      <c r="B264" s="1" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="265" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A265" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="B265" s="1" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A266" s="4"/>
-    </row>
-    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A267" s="4"/>
-    </row>
+      <c r="A244" s="2"/>
+    </row>
+    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A245" s="2"/>
+    </row>
+    <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4483,17 +4733,17 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.51171875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="120.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>

--- a/data/raw/rules/translations.xlsx
+++ b/data/raw/rules/translations.xlsx
@@ -2235,7 +2235,7 @@
   <si>
     <t xml:space="preserve">When a &lt;b&gt;Monster&lt;/b&gt; wishes to use this Brutal Power Attack, it must nominate a single enemy model involved in the Combat before models Back Away – this is the model that will be Hurled. A &lt;b&gt;Monster&lt;/b&gt; cannot nominate a model to be Hurled that has a Strength equal to or higher than their own. Then, all other enemy models (not the nominated model) Back Away as normal. The Monster will then Hurl the nominated model.
 To Hurl a model, follow the steps below:
-&lt;ul&gt;
+&lt;ol&gt;
 &lt;li&gt; The &lt;b&gt;Monster&lt;/b&gt; rolls a D3 and adds the difference in Strength between the &lt;b&gt;Monster&lt;/b&gt; and the nominated model – this is the Hurl Distance.&lt;/li&gt;
 &lt;li&gt;The &lt;b&gt;Monster&lt;/b&gt; must then take an Intelligence Test (if the &lt;b&gt;Monster&lt;/b&gt; is also a &lt;b&gt;Mount&lt;/b&gt;, it may use the Intelligence of its rider if it is better).&lt;/li&gt;
 &lt;li&gt;If the test is passed, the &lt;b&gt;Monster&lt;/b&gt; chooses an enemy model it can draw Line of Sight to, and within the Hurl Distance from itself, to Hurl the nominated model at – this is the target. A model can only be chosen as the target of a Hurl once per turn. If the test was failed, the opposing player may choose one of their models in Line of Sight of the &lt;b&gt;Monster&lt;/b&gt;, and within the Hurl Distance, to be the target instead.&lt;/li&gt;
@@ -2244,7 +2244,7 @@
 &lt;li&gt;The target model is then knocked Prone, if it has a Strength of 5 or less, and will suffer one Strength 6 hit (if it is a &lt;b&gt;Cavalry&lt;/b&gt; model then both rider and &lt;b&gt;Mount&lt;/b&gt; will suffer these hits). If it is a &lt;b&gt;Cavalry&lt;/b&gt; model then it is also Knocked Flying.&lt;/li&gt;
 &lt;li&gt;If there are no enemy models eligible to be the target, then the &lt;b&gt;Monster&lt;/b&gt; may choose a point on the battlefield it can draw Line of Sight within the Hurl Distance instead. Place the Hurled model on the chosen point; it is then knocked Prone and suffers two Strength 6 hits.&lt;/li&gt;
 &lt;li&gt;Once a &lt;b&gt;Monster&lt;/b&gt; model has used a Hurl, the Combat immediately ends and no further Strikes or Brutal Power Attacks can be made. A Monster cannot Hurl in the same turn in which it participates in a Heroic Combat.&lt;/li&gt;
-&lt;/ul&gt;</t>
+&lt;/ol&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">hand-weapon.name</t>
@@ -2375,10 +2375,38 @@
     <t xml:space="preserve">elven-weapon.description</t>
   </si>
   <si>
-    <t xml:space="preserve">Some weapons will be described as an Elven weapon; for example, a model may have an Elven hand weapon or an Elven two-handed weapon.
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Some weapons will be described as an Elven weapon; for example, a model may have an Elven &lt;rule id="hand-weapon"&gt;hand weapon&lt;/rule&gt; or an Elven </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">&lt;rule id="two-handed-hand-weapon"&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">two-handed weapon&lt;/rule&gt;.
 If a model fights with an Elven weapon in a Combat, they will be more likely to win the Duel Roll in the result of a Drawn Combat. In these instances, a Good model armed with an Elven weapon will win the roll-off ona 3+, whilst an Evil model armed with an Elven weapon will win the roll-off on a 1-4. If both sides have an Elven weapon, neither side gains the benefit.
 Some Missile Weapons may also be classed as Elven weapons; however, the above bonus only applies to Melee Weapons as a model cannot choose to fight with a Missile Weapon in a Combat.
 Any weapon with the word ‘Elf’ in its name is automatically considered to be an Elven weapon.</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">master-forged.name</t>
@@ -2428,7 +2456,7 @@
   </si>
   <si>
     <t xml:space="preserve">A model with a throwing weapon can make a Shooting Attack with it in the Shoot Phase, even if it Moved its full Move Value in the preceding Move Phase.
-Alternatively, once per turn, a model may make a Shooting Attack with a throwing weapon during the Move Phaseas it Charges an enemy model. If a model wishes to use a throwing weapon in this manner, then when it Charges it will stop 1" away from the model it wishes to Charge, andthen make a Shooting Attack against the model. If the model using the throwing weapon begins its Move within the Control Zone of an enemy model it wishes to Charge, then it doesn’t need to Move first before throwing the weapon. This is made using all the normal rules for a Shooting Attack, with the exception of that throwing weapons thrown in this manner do not suffer the -1 penalty To Hit for Moving and Shooting.
+Alternatively, once per turn, a model may make a Shooting Attack with a throwing weapon during the Move Phase as it Charges an enemy model. If a model wishes to use a throwing weapon in this manner, then when it Charges it will stop 1" away from the model it wishes to Charge, and then make a Shooting Attack against the model. If the model using the throwing weapon begins its Move within the Control Zone of an enemy model it wishes to Charge, then it doesn’t need to Move first before throwing the weapon. This is made using all the normal rules for a Shooting Attack, with the exception of that throwing weapons thrown in this manner do not suffer the -1 penalty To Hit for Moving and Shooting.
 If the target is not slain, then the model continues their Charge as normal and must Charge the target of their Shooting Attack. If the target is slain, then the model may continue to Move as normal, and may even Charge a different target if they wish.
 Throwing weapons do not count towards an Army’s Bow Limit. However, an Army can only have one third of its models armed with throwing weapons, unless specifically stated otherwise.
 Throwing spears follow the same rules as throwing weapons, but have a slightly different profile, as shown on the Missile Weapon Chart.</t>
@@ -2498,7 +2526,7 @@
     <t xml:space="preserve">elven-cloak.description</t>
   </si>
   <si>
-    <t xml:space="preserve">A model wearing an Elven cloak has the Stalk Unseen special rule. Additionally, models targeting an &lt;b&gt;Infantry&lt;/b&gt; model wearing an Elven cloak with a Shooting Attack suffer a -1 penalty when rolling To Hit.</t>
+    <t xml:space="preserve">A model wearing an Elven cloak has the &lt;rule id="stalk-unseen"&gt;Stalk Unseen&lt;/rule&gt; special rule. Additionally, models targeting an &lt;b&gt;Infantry&lt;/b&gt; model wearing an Elven cloak with a Shooting Attack suffer a -1 penalty when rolling To Hit.</t>
   </si>
   <si>
     <t xml:space="preserve">war-drum.name</t>
@@ -4392,7 +4420,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="142.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="157.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="2" t="s">
         <v>412</v>
       </c>

--- a/data/raw/rules/translations.xlsx
+++ b/data/raw/rules/translations.xlsx
@@ -110,92 +110,7 @@
     <t xml:space="preserve">banishment.description</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">This Magical Power targets one enemy &lt;b&gt;Spirit&lt;/b&gt; model within range. The target immediately suffers 1 Wound. If this Magical Power targets a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Cavalry</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;/b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> model, the caster must choose whether the rider or the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Mount</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;/b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> is the target.</t>
-    </r>
+    <t xml:space="preserve">This Magical Power targets one enemy &lt;b&gt;Spirit&lt;/b&gt; model within range. The target immediately suffers 1 Wound. If this Magical Power targets a &lt;b&gt;Cavalry&lt;/b&gt; model, the caster must choose whether the rider or the &lt;b&gt;Mount&lt;/b&gt; is the target.</t>
   </si>
   <si>
     <t xml:space="preserve">black-dart.name</t>
@@ -207,92 +122,7 @@
     <t xml:space="preserve">black-dart.description</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">This Magical Power targets one enemy model within range. The target immediately suffers one Strength 6 hit. If this Magical Power targets a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Cavalry</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;/b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> model, the caster must choose whether the rider or the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Mount</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;/b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> is the target.</t>
-    </r>
+    <t xml:space="preserve">This Magical Power targets one enemy model within range. The target immediately suffers one Strength 6 hit. If this Magical Power targets a &lt;b&gt;Cavalry&lt;/b&gt; model, the caster must choose whether the rider or the &lt;b&gt;Mount&lt;/b&gt; is the target.</t>
   </si>
   <si>
     <t xml:space="preserve">blades-of-the-dead.name</t>
@@ -401,92 +231,7 @@
     <t xml:space="preserve">chill-soul.description</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">This Magical Power targets one enemy model in range. The target immediately suffers 1 Wound. If this Magical Power targets a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Cavalry</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;/b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> model, the caster must choose whether the rider or the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Mount</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;/b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> is the target.</t>
-    </r>
+    <t xml:space="preserve">This Magical Power targets one enemy model in range. The target immediately suffers 1 Wound. If this Magical Power targets a &lt;b&gt;Cavalry&lt;/b&gt; model, the caster must choose whether the rider or the &lt;b&gt;Mount&lt;/b&gt; is the target.</t>
   </si>
   <si>
     <t xml:space="preserve">collapse-rocks.name</t>
@@ -522,92 +267,7 @@
     <t xml:space="preserve">curse.description</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">This Magical Power targets one enemy model in range. The target immediately loses 1 Fate Point. If this Magical Power targets a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Cavalry</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;/b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> model, the caster must choose whether the rider or the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Mount</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;/b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> is the target.</t>
-    </r>
+    <t xml:space="preserve">This Magical Power targets one enemy model in range. The target immediately loses 1 Fate Point. If this Magical Power targets a &lt;b&gt;Cavalry&lt;/b&gt; model, the caster must choose whether the rider or the &lt;b&gt;Mount&lt;/b&gt; is the target.</t>
   </si>
   <si>
     <t xml:space="preserve">dominant.name</t>
@@ -632,92 +292,7 @@
     <t xml:space="preserve">drain-courage.description</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">This Magical Power targets one enemy model in range. The target immediately worsens their Courage value by 1 for the remainder of the game; so a model with a Courage of 5+ that is affected by this Magical Power would then have a Courage of 6+. A model can be affected by this Magical Power multiple times over the course of the battle, worsening its Courage value each time. If this Magical Power targets a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Cavalry</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;/b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> model, the caster must choose whether the rider or the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Mount</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;/b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> is the target.</t>
-    </r>
+    <t xml:space="preserve">This Magical Power targets one enemy model in range. The target immediately worsens their Courage value by 1 for the remainder of the game; so a model with a Courage of 5+ that is affected by this Magical Power would then have a Courage of 6+. A model can be affected by this Magical Power multiple times over the course of the battle, worsening its Courage value each time. If this Magical Power targets a &lt;b&gt;Cavalry&lt;/b&gt; model, the caster must choose whether the rider or the &lt;b&gt;Mount&lt;/b&gt; is the target.</t>
   </si>
   <si>
     <t xml:space="preserve">enchant-blades.name</t>
@@ -741,54 +316,7 @@
     <t xml:space="preserve">enrage-beast.description</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">This Magical Power targets one friendly </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Beast</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;/b&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">model within range. The target increases its Fight Value, Strength and Attacks by 2, and gains the Fearless special rule, until the End Phase of the turn, at which point the target will immediately suffer 1 Wound.</t>
-    </r>
+    <t xml:space="preserve">This Magical Power targets one friendly &lt;b&gt;Beast&lt;/b&gt; model within range. The target increases its Fight Value, Strength and Attacks by 2, and gains the Fearless special rule, until the End Phase of the turn, at which point the target will immediately suffer 1 Wound.</t>
   </si>
   <si>
     <t xml:space="preserve">expert-rider.name</t>
@@ -1265,54 +793,7 @@
     <t xml:space="preserve">natures-wrath.description</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">This Magical Power targets all enemy models within range, even if they are not in Line of Sight of the caster. All targets models are immediately knocked Prone. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Cavalry</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;/b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> models are automatically treated as suffering a Knocked Flying result on the Thrown Rider Chart.</t>
-    </r>
+    <t xml:space="preserve">This Magical Power targets all enemy models within range, even if they are not in Line of Sight of the caster. All targets models are immediately knocked Prone. &lt;b&gt;Cavalry&lt;/b&gt; models are automatically treated as suffering a Knocked Flying result on the Thrown Rider Chart.</t>
   </si>
   <si>
     <t xml:space="preserve">panic-steed.name</t>
@@ -1324,92 +805,7 @@
     <t xml:space="preserve">panic-steed.description</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">This Magical Power targets one enemy </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Cavalry</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;/b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> model within range. The rider is thrown and the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Mount</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;/b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> immediately flees and is removed as a casualty. The rider is automatically treated as suffering a Knocked Flying result on the Thrown Rider Chart.</t>
-    </r>
+    <t xml:space="preserve">This Magical Power targets one enemy &lt;b&gt;Cavalry&lt;/b&gt; model within range. The rider is thrown and the &lt;b&gt;Mount&lt;/b&gt; immediately flees and is removed as a casualty. The rider is automatically treated as suffering a Knocked Flying result on the Thrown Rider Chart.</t>
   </si>
   <si>
     <t xml:space="preserve">paralyse.name</t>
@@ -1460,92 +856,7 @@
     <t xml:space="preserve">renew.description</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">This Magical Power targets one friendly model in range. The target immediately regains 1 Wound lost earlier in the battle. If this Magical Power targets a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Cavalry</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;/b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> model, the caster must choose whether the rider or the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Mount</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;/b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> is the target.</t>
-    </r>
+    <t xml:space="preserve">This Magical Power targets one friendly model in range. The target immediately regains 1 Wound lost earlier in the battle. If this Magical Power targets a &lt;b&gt;Cavalry&lt;/b&gt; model, the caster must choose whether the rider or the &lt;b&gt;Mount&lt;/b&gt; is the target.</t>
   </si>
   <si>
     <t xml:space="preserve">resistant-to-magic.name</t>
@@ -1608,55 +919,8 @@
     <t xml:space="preserve">sorcerous-blast.description</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">This Magical Power targets one enemy model in range. The target immediately suffers one Strength 5 hit. If they survive, they are immediately knocked Prone. If the target was a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Cavalry</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;/b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> model, they will automatically count as suffering the Knocked Flying result on the Thrown Rider Chart.
+    <t xml:space="preserve">This Magical Power targets one enemy model in range. The target immediately suffers one Strength 5 hit. If they survive, they are immediately knocked Prone. If the target was a &lt;b&gt;Cavalry&lt;/b&gt; model, they will automatically count as suffering the Knocked Flying result on the Thrown Rider Chart.
 If the target was Engaged in Combat, then any other model that's also Engaged in the same Combat will also be knocked Prone if it has a Strength of 5 or lower - make sure to Pair Off Combats before working out which models are knocked Prone in this manner.</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">spectral-walk.name</t>
@@ -1692,92 +956,7 @@
     <t xml:space="preserve">strengthen-will.description</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">This Magical Power targets one friendly model within range. The target immediately regains a single Will Point spent earlier in the battle. If this Magical Power targets a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Cavalry</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;/b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> model, the caster must choose whether the rider or the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Mount</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;/b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> is the target.</t>
-    </r>
+    <t xml:space="preserve">This Magical Power targets one friendly model within range. The target immediately regains a single Will Point spent earlier in the battle. If this Magical Power targets a &lt;b&gt;Cavalry&lt;/b&gt; model, the caster must choose whether the rider or the &lt;b&gt;Mount&lt;/b&gt; is the target.</t>
   </si>
   <si>
     <t xml:space="preserve">survival-instinct.name</t>
@@ -1888,55 +1067,8 @@
     <t xml:space="preserve">tremor.description</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Draw an imaginary 1mm line that extends D3+3" directly away from the caster in a direction chosen by the caster. This Magical Power targets every model (friend or foe) that lies under the line. Each target immediately suffers one Strength 4 hit and is knocked Prone; if the target was a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Cavalry</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;/b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> model, they will automatically count as suffering the Knocked Flying result on the Thrown Rider Chart. If a target is Engaged in Combat, then any other model Engaged in the same Combat is also considered to be a target - make sure to Pair Off Combats before working out which models are targets. 
+    <t xml:space="preserve">Draw an imaginary 1mm line that extends D3+3" directly away from the caster in a direction chosen by the caster. This Magical Power targets every model (friend or foe) that lies under the line. Each target immediately suffers one Strength 4 hit and is knocked Prone; if the target was a &lt;b&gt;Cavalry&lt;/b&gt; model, they will automatically count as suffering the Knocked Flying result on the Thrown Rider Chart. If a target is Engaged in Combat, then any other model Engaged in the same Combat is also considered to be a target - make sure to Pair Off Combats before working out which models are targets. 
 Models with the &lt;rule id="fly"&gt;Fly&lt;/rule&gt; special rule can never be a target of this Magical Power under any circumstances.</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">unyielding-combat-stance.name</t>
@@ -1985,73 +1117,7 @@
     <t xml:space="preserve">wither.description</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">This Magical Power targets one enemy model in range. The target immediately reduces their Strength value by 1 for the remainder of the game. A model can be affected by this Magical Power multiple times over the course of the battle, reducing its Strength value each time. Should a model ever have its Strength reduced to 0, they are immediately slain and removed as a casualty. If this Magical Power targets a &lt;b&gt;Cavalry</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;/b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> model, the caster must choose whether the rider or the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Mount</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;/b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> is the target.</t>
-    </r>
+    <t xml:space="preserve">This Magical Power targets one enemy model in range. The target immediately reduces their Strength value by 1 for the remainder of the game. A model can be affected by this Magical Power multiple times over the course of the battle, reducing its Strength value each time. Should a model ever have its Strength reduced to 0, they are immediately slain and removed as a casualty. If this Magical Power targets a &lt;b&gt;Cavalry&lt;/b&gt; model, the caster must choose whether the rider or the &lt;b&gt;Mount&lt;/b&gt; is the target.</t>
   </si>
   <si>
     <t xml:space="preserve">woodland-creature.name</t>
@@ -2075,54 +1141,7 @@
     <t xml:space="preserve">wrath-of-bruinen.description</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">This Magical Power targets all enemy models within range, even if they are not in Line of Sight of the caster. All target models immediately suffer one Strength 2 hit and are knocked Prone. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Cavalry</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;/b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> models are automatically treated as suffering a Knocked Flying result on the Thrown Rider Chart. If a target is within a water feature, they will suffer one Strength 8 hit instead of one Strength 2 hit.</t>
-    </r>
+    <t xml:space="preserve">This Magical Power targets all enemy models within range, even if they are not in Line of Sight of the caster. All target models immediately suffer one Strength 2 hit and are knocked Prone. &lt;b&gt;Cavalry&lt;/b&gt; models are automatically treated as suffering a Knocked Flying result on the Thrown Rider Chart. If a target is within a water feature, they will suffer one Strength 8 hit instead of one Strength 2 hit.</t>
   </si>
   <si>
     <t xml:space="preserve">writhing-vines.name</t>
@@ -2170,58 +1189,11 @@
     <t xml:space="preserve">barge.description</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">When a &lt;b&gt;Monster&lt;/b&gt; wishes to use this Brutal Power Attack, enemy models do not Back Away as normal. Instead, all enemy models involved in the Combat, plus any enemy models that were Supporting, must Back Away 3" rather than 1". The order and direction that these models Back Away is chosen by the &lt;b&gt;Monster&lt;/b&gt; model’s controlling player. Models may still Make Way for losing models (which will be decided by the &lt;b&gt;Monster&lt;/b&gt; model’s controlling player) and, if they do, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;u&gt;may&lt;/u&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> Make Way 3" rather than the usual 1", in a direction chosen by the &lt;b&gt;Monster&lt;/b&gt; model’s controlling player. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;u&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">When a model Makes Way in this manner, it will only do so the minimum amount it needs to in order to allow the model Backing Away to Back Away 3"; it won’t be forced to Make Way a full 3" if only Making Way 1" would suffice to allow the Barged model to Back Away 3", for example, and won’t be automatically knocked Prone if it is able to Make Way the required amount.&lt;/u&gt;
+    <t xml:space="preserve">When a &lt;b&gt;Monster&lt;/b&gt; wishes to use this Brutal Power Attack, enemy models do not Back Away as normal. Instead, all enemy models involved in the Combat, plus any enemy models that were Supporting, must Back Away 3" rather than 1". The order and direction that these models Back Away is chosen by the &lt;b&gt;Monster&lt;/b&gt; model’s controlling player. Models may still Make Way for losing models (which will be decided by the &lt;b&gt;Monster&lt;/b&gt; model’s controlling player) and, if they do, &lt;u&gt;may&lt;/u&gt; Make Way 3" rather than the usual 1", in a direction chosen by the &lt;b&gt;Monster&lt;/b&gt; model’s controlling player. &lt;u&gt;When a model Makes Way in this manner, it will only do so the minimum amount it needs to in order to allow the model Backing Away to Back Away 3"; it won’t be forced to Make Way a full 3" if only Making Way 1" would suffice to allow the Barged model to Back Away 3", for example, and won’t be automatically knocked Prone if it is able to Make Way the required amount.&lt;/u&gt;
 Any models that cannot Back Away or Make Way the full 3" are moved as far as possible and then knocked Prone. When doing this, if it is possible for a &lt;b&gt;Monster&lt;/b&gt; to choose a direction for a model to Back Away or Make Way so that it goes the full 3", then it must choose that direction–it can’t force a model to Back Away or Make Way less than 3" and be knocked Prone if there was a way for it to Back Away the full 3".
 Once a &lt;b&gt;Monster&lt;/b&gt; model has used a Barge, the Combat immediately ends and no further Strikes or Brutal Power Attacks can be made.
 Once all models have Backed Away, the &lt;b&gt;Monster&lt;/b&gt; that made the Barge can then Move D3+3" in any direction, following all the usual rules for Moving a model. It can even Charge again if it wishes, in which case it will fight again that Fight Phase in the ordinary way – i.e., in an order chosen by the player with Priority.
 A &lt;b&gt;Monster&lt;/b&gt; cannot Barge in the same turn in which it participates in a Heroic Combat.</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">hurl.name</t>
@@ -2375,38 +1347,10 @@
     <t xml:space="preserve">elven-weapon.description</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Some weapons will be described as an Elven weapon; for example, a model may have an Elven &lt;rule id="hand-weapon"&gt;hand weapon&lt;/rule&gt; or an Elven </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;rule id="two-handed-hand-weapon"&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">two-handed weapon&lt;/rule&gt;.
+    <t xml:space="preserve">Some weapons will be described as an Elven weapon; for example, a model may have an Elven &lt;rule id="hand-weapon"&gt;hand weapon&lt;/rule&gt; or an Elven &lt;rule id="two-handed-hand-weapon"&gt;two-handed weapon&lt;/rule&gt;.
 If a model fights with an Elven weapon in a Combat, they will be more likely to win the Duel Roll in the result of a Drawn Combat. In these instances, a Good model armed with an Elven weapon will win the roll-off ona 3+, whilst an Evil model armed with an Elven weapon will win the roll-off on a 1-4. If both sides have an Elven weapon, neither side gains the benefit.
 Some Missile Weapons may also be classed as Elven weapons; however, the above bonus only applies to Melee Weapons as a model cannot choose to fight with a Missile Weapon in a Combat.
 Any weapon with the word ‘Elf’ in its name is automatically considered to be an Elven weapon.</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">master-forged.name</t>
@@ -2633,7 +1577,7 @@
 A shield is cumbersome, and so a model carrying a shield that wishes to use their &lt;rule id="hand-and-a-half-weapon"&gt;hand-and-a-half weapon&lt;/rule&gt; as a &lt;rule id="two-handed-weapon"&gt;two-handed weapon&lt;/rule&gt; during a Combat cannot gain the Defence bonus for carrying a shield during that Combat. Additionally, a model carrying a shield does not gain the Defence bonus if it also carries a type of bow, crossbow, two-handed weapon or &lt;rule id="pike"&gt;pike&lt;/rule&gt;.
 A model with a shield can also use the Shielding special rule:
 &lt;h3&gt;Shielding&lt;/h3&gt;
-A model carrying a shield may declare they are Shielding at the start of a Combat they are involved in, before the Duel Roll is made. If they do, the Shielding model will double their Attacks characteristic for the duration of the Combat; however, if they win the Duel Roll they cannot make Strikes having put their effort into surviving. &lt;u&gt;They also don’t gain any advantages of the special rules of their weapons (such as if they have an Elven weapon) as they are not using them in the Combat and are using their shield instead.&lt;/u&gt;
+A model carrying a shield may declare they are Shielding at the start of a Combat they are involved in, before the Duel Roll is made. If they do, the Shielding model will double their Attacks characteristic for the duration of the Combat; however, if they win the Duel Roll they cannot make Strikes having put their effort into surviving. They also don’t gain any advantages of the special rules of their weapons (such as if they have an Elven weapon) as they are not using them in the Combat and are using their shield instead.
 In a Multiple Combat, if one model wishes to declare they are Shielding, then all friendly models must do so. If some of them cannot, then no models may declare they are Shielding. Models that are Shielding cannot be Supported.
 &lt;b&gt;Cavalry&lt;/b&gt; models cannot declare they are Shielding. Additionally, Shielding is treated as an Active ability (see page 123).
 A Prone model can declare they are Shielding – infact, it is a sensible way of trying to get them to stand backup as a Prone model can’t make Strikes anyway!</t>
@@ -2658,7 +1602,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -2680,12 +1624,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -4761,7 +3699,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="8.51171875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.51953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="120.83"/>

--- a/data/raw/rules/translations.xlsx
+++ b/data/raw/rules/translations.xlsx
@@ -8,8 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="en" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="nl" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Translations" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,12 +20,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="487">
   <si>
     <t xml:space="preserve">key</t>
   </si>
   <si>
-    <t xml:space="preserve">translation</t>
+    <t xml:space="preserve">en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nl</t>
   </si>
   <si>
     <t xml:space="preserve">ancient-enemies.name</t>
@@ -1668,7 +1670,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1679,10 +1681,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1702,11 +1700,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B1048576"/>
+  <dimension ref="A1:C245"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="48.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="120.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="61.74"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="3" style="1" width="8.5"/>
   </cols>
   <sheetData>
@@ -1717,1941 +1715,1944 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="71.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="86.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="71.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="114.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="100.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="171.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="86.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="86.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="100.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="185.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="86.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="142.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="114.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="71.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="71.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="256.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="440.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="71.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="71.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="71.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="199.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="313.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="270.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="455.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="213.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="341.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="86.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="384.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="610.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="497.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="767.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="128.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="228.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="157.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="242" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="71.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="270.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="412.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="100.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="114.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="100.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="100.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="157.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="157.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="270.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="86.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="135" customFormat="false" ht="100.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="142.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="137" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="100.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="139" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="100.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="141" customFormat="false" ht="86.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="142.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="143" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="145" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="71.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="147" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="149" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="71.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="151" customFormat="false" ht="86.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="142.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="153" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="157" customFormat="false" ht="171.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="284.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="159" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="161" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="86.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="163" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="86.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="165" customFormat="false" ht="100.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="171.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="167" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="100.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="169" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="171" customFormat="false" ht="114.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="199.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="173" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="114.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="175" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="114.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="177" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="86.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="179" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="181" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="183" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="114.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="185" customFormat="false" ht="270.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="483.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="187" customFormat="false" ht="369.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="653.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="189" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="71.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="191" customFormat="false" ht="114.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="199.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="193" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="71.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="195" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="100.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="197" customFormat="false" ht="313.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="483.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="199" customFormat="false" ht="199.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="284.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="201" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="100.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="203" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="71.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="207" customFormat="false" ht="157.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="228.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="209" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="211" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="213" customFormat="false" ht="86.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="142.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="215" customFormat="false" ht="228.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="369.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="219" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="86.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="221" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="86.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="223" customFormat="false" ht="412.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="667.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="225" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="227" customFormat="false" ht="157.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="270.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="229" customFormat="false" ht="71.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="128.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="233" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="237" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="239" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="239" customFormat="false" ht="57.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="241" customFormat="false" ht="327.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="483.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="243" customFormat="false" ht="29.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="43.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3659,59 +3660,6 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="2"/>
-    </row>
-    <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="8.51953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="120.83"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
